--- a/es/es-global-request-prev.xlsx
+++ b/es/es-global-request-prev.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cnxmail-my.sharepoint.com/personal/sujeong_kang_concentrix_com/Documents/02.Operations/01.BU/01.ES/00.Dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="89" documentId="8_{FF890E52-4AAD-4F12-9508-254A9223DFED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4CA27A67-1F14-41F3-A38E-AA1573948DDE}"/>
+  <xr:revisionPtr revIDLastSave="158" documentId="8_{FF890E52-4AAD-4F12-9508-254A9223DFED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D8D3F71B-B237-4256-A899-E7BA2134B521}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LG DUALCOOL AI" sheetId="2" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12440" uniqueCount="2254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12628" uniqueCount="2263">
   <si>
     <t>Title</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -6484,9 +6484,6 @@
     <t>09/10/2026</t>
   </si>
   <si>
-    <t>페이지 확인중</t>
-  </si>
-  <si>
     <t>09/11/2026</t>
   </si>
   <si>
@@ -6926,10 +6923,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>사전검토</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>우선 제외</t>
   </si>
   <si>
@@ -6941,6 +6934,97 @@
   </si>
   <si>
     <t>작업중</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>페이지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>확인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>불가</t>
+    </r>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>09/21/2026</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>09/16/2026</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>09/18/2026</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>취소</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>10/08/2026</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>완료</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>09/21/2026</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>09/22/2026</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>09/23/2026</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>09/28/2026</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -6948,7 +7032,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9">
+  <fonts count="11">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -7013,6 +7097,19 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -7042,7 +7139,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -7061,6 +7158,7 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -7555,7 +7653,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>2243</v>
+        <v>2242</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.5">
@@ -26545,7 +26643,7 @@
         <v>1191</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>2249</v>
+        <v>2251</v>
       </c>
       <c r="F8" s="1"/>
       <c r="G8" s="1">
@@ -26569,7 +26667,7 @@
         <v>1194</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>2249</v>
+        <v>2251</v>
       </c>
       <c r="F9" s="1"/>
       <c r="G9" s="1">
@@ -26590,7 +26688,7 @@
         <v>1195</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>2249</v>
+        <v>2251</v>
       </c>
       <c r="F10" s="1"/>
       <c r="G10" s="1">
@@ -26611,7 +26709,7 @@
         <v>1196</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>2249</v>
+        <v>2251</v>
       </c>
       <c r="F11" s="1"/>
       <c r="G11" s="1">
@@ -26632,7 +26730,7 @@
         <v>1197</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>2249</v>
+        <v>2251</v>
       </c>
       <c r="F12" s="1"/>
       <c r="G12" s="1">
@@ -26653,7 +26751,7 @@
         <v>1191</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>2253</v>
+        <v>2251</v>
       </c>
       <c r="F13" s="1"/>
       <c r="G13" s="1">
@@ -26677,7 +26775,7 @@
         <v>1194</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>2253</v>
+        <v>2251</v>
       </c>
       <c r="F14" s="1"/>
       <c r="G14" s="1">
@@ -26698,7 +26796,7 @@
         <v>1195</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>2253</v>
+        <v>2251</v>
       </c>
       <c r="F15" s="1"/>
       <c r="G15" s="1">
@@ -26719,7 +26817,7 @@
         <v>1196</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>2253</v>
+        <v>2251</v>
       </c>
       <c r="F16" s="1"/>
       <c r="G16" s="1">
@@ -26740,7 +26838,7 @@
         <v>1197</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>2253</v>
+        <v>2251</v>
       </c>
       <c r="F17" s="1"/>
       <c r="G17" s="1">
@@ -26883,7 +26981,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>2244</v>
+        <v>2243</v>
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -26894,7 +26992,7 @@
         <v>1182</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>2248</v>
+        <v>2247</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -27391,14 +27489,14 @@
         <v>1</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>1590</v>
+        <v>2256</v>
       </c>
       <c r="H22" s="6" t="s">
         <v>2109</v>
       </c>
       <c r="I22" s="6"/>
-      <c r="J22" t="s">
-        <v>2111</v>
+      <c r="J22" s="14" t="s">
+        <v>2252</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="13.5">
@@ -28065,7 +28163,7 @@
         <v>2109</v>
       </c>
       <c r="I45" s="6" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
     </row>
     <row r="46" spans="1:9" ht="13.5">
@@ -28094,7 +28192,7 @@
         <v>2109</v>
       </c>
       <c r="I46" s="6" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
     </row>
     <row r="47" spans="1:9" ht="13.5">
@@ -28123,7 +28221,7 @@
         <v>2109</v>
       </c>
       <c r="I47" s="6" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
     </row>
     <row r="48" spans="1:9" ht="13.5">
@@ -28152,7 +28250,7 @@
         <v>2109</v>
       </c>
       <c r="I48" s="6" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
     </row>
     <row r="49" spans="1:9" ht="13.5">
@@ -28181,7 +28279,7 @@
         <v>2109</v>
       </c>
       <c r="I49" s="6" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
     </row>
     <row r="50" spans="1:9" ht="13.5">
@@ -28210,7 +28308,7 @@
         <v>2109</v>
       </c>
       <c r="I50" s="6" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
     </row>
     <row r="51" spans="1:9" ht="13.5">
@@ -28239,7 +28337,7 @@
         <v>2109</v>
       </c>
       <c r="I51" s="6" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
     </row>
     <row r="52" spans="1:9" ht="13.5">
@@ -28268,7 +28366,7 @@
         <v>2109</v>
       </c>
       <c r="I52" s="6" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
     </row>
     <row r="53" spans="1:9" ht="13.5">
@@ -28297,7 +28395,7 @@
         <v>2109</v>
       </c>
       <c r="I53" s="6" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
     </row>
     <row r="54" spans="1:9" ht="13.5">
@@ -28326,7 +28424,7 @@
         <v>2109</v>
       </c>
       <c r="I54" s="6" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
     </row>
     <row r="55" spans="1:9" ht="13.5">
@@ -28355,7 +28453,7 @@
         <v>2109</v>
       </c>
       <c r="I55" s="6" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
     </row>
     <row r="56" spans="1:9" ht="13.5">
@@ -28384,7 +28482,7 @@
         <v>2109</v>
       </c>
       <c r="I56" s="6" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
     </row>
     <row r="57" spans="1:9" ht="13.5">
@@ -28413,7 +28511,7 @@
         <v>2109</v>
       </c>
       <c r="I57" s="6" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
     </row>
     <row r="58" spans="1:9" ht="13.5">
@@ -28442,7 +28540,7 @@
         <v>2109</v>
       </c>
       <c r="I58" s="6" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
     </row>
     <row r="59" spans="1:9" ht="13.5">
@@ -28471,7 +28569,7 @@
         <v>2109</v>
       </c>
       <c r="I59" s="6" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
     </row>
     <row r="60" spans="1:9" ht="13.5">
@@ -28500,7 +28598,7 @@
         <v>2109</v>
       </c>
       <c r="I60" s="6" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
     </row>
     <row r="61" spans="1:9" ht="13.5">
@@ -28529,7 +28627,7 @@
         <v>2109</v>
       </c>
       <c r="I61" s="6" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
     </row>
     <row r="62" spans="1:9" ht="13.5">
@@ -28558,7 +28656,7 @@
         <v>2109</v>
       </c>
       <c r="I62" s="6" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
     </row>
     <row r="63" spans="1:9" ht="13.5">
@@ -28587,7 +28685,7 @@
         <v>2109</v>
       </c>
       <c r="I63" s="6" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
     </row>
     <row r="64" spans="1:9" ht="13.5">
@@ -28616,7 +28714,7 @@
         <v>2109</v>
       </c>
       <c r="I64" s="6" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
     </row>
     <row r="65" spans="1:9" ht="13.5">
@@ -28645,7 +28743,7 @@
         <v>2109</v>
       </c>
       <c r="I65" s="6" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
     </row>
     <row r="66" spans="1:9" ht="13.5">
@@ -28674,7 +28772,7 @@
         <v>2109</v>
       </c>
       <c r="I66" s="6" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
     </row>
     <row r="67" spans="1:9" ht="13.5">
@@ -28703,7 +28801,7 @@
         <v>2109</v>
       </c>
       <c r="I67" s="6" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
     </row>
     <row r="68" spans="1:9" ht="13.5">
@@ -28732,7 +28830,7 @@
         <v>2109</v>
       </c>
       <c r="I68" s="6" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
     </row>
     <row r="69" spans="1:9" ht="13.5">
@@ -28761,7 +28859,7 @@
         <v>2109</v>
       </c>
       <c r="I69" s="6" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
     </row>
     <row r="70" spans="1:9" ht="13.5">
@@ -28790,7 +28888,7 @@
         <v>2109</v>
       </c>
       <c r="I70" s="6" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
     </row>
     <row r="71" spans="1:9" ht="13.5">
@@ -28819,7 +28917,7 @@
         <v>2109</v>
       </c>
       <c r="I71" s="6" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
     </row>
     <row r="72" spans="1:9" ht="13.5">
@@ -28848,7 +28946,7 @@
         <v>2109</v>
       </c>
       <c r="I72" s="6" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
     </row>
     <row r="73" spans="1:9" ht="13.5">
@@ -28877,7 +28975,7 @@
         <v>2109</v>
       </c>
       <c r="I73" s="6" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
     </row>
     <row r="74" spans="1:9" ht="13.5">
@@ -28906,7 +29004,7 @@
         <v>2109</v>
       </c>
       <c r="I74" s="6" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
     </row>
     <row r="75" spans="1:9" ht="13.5">
@@ -28935,7 +29033,7 @@
         <v>2109</v>
       </c>
       <c r="I75" s="6" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
     </row>
     <row r="76" spans="1:9" ht="13.5">
@@ -28964,7 +29062,7 @@
         <v>2109</v>
       </c>
       <c r="I76" s="6" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
     </row>
     <row r="77" spans="1:9" ht="13.5">
@@ -28993,7 +29091,7 @@
         <v>2109</v>
       </c>
       <c r="I77" s="6" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
     </row>
     <row r="78" spans="1:9" ht="13.5">
@@ -29022,7 +29120,7 @@
         <v>2109</v>
       </c>
       <c r="I78" s="6" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
     </row>
     <row r="79" spans="1:9" ht="13.5">
@@ -29051,7 +29149,7 @@
         <v>2109</v>
       </c>
       <c r="I79" s="6" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
     </row>
     <row r="80" spans="1:9" ht="13.5">
@@ -29080,7 +29178,7 @@
         <v>2109</v>
       </c>
       <c r="I80" s="6" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
     </row>
     <row r="81" spans="1:9" ht="13.5">
@@ -29109,7 +29207,7 @@
         <v>2109</v>
       </c>
       <c r="I81" s="6" t="s">
-        <v>2113</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="82" spans="1:9" ht="13.5">
@@ -29138,7 +29236,7 @@
         <v>2109</v>
       </c>
       <c r="I82" s="6" t="s">
-        <v>2113</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="83" spans="1:9" ht="13.5">
@@ -29167,7 +29265,7 @@
         <v>2109</v>
       </c>
       <c r="I83" s="6" t="s">
-        <v>2113</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="84" spans="1:9" ht="13.5">
@@ -29196,7 +29294,7 @@
         <v>2109</v>
       </c>
       <c r="I84" s="6" t="s">
-        <v>2113</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="85" spans="1:9" ht="13.5">
@@ -29225,7 +29323,7 @@
         <v>2109</v>
       </c>
       <c r="I85" s="6" t="s">
-        <v>2113</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="86" spans="1:9" ht="13.5">
@@ -29254,7 +29352,7 @@
         <v>2109</v>
       </c>
       <c r="I86" s="6" t="s">
-        <v>2113</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="87" spans="1:9" ht="13.5">
@@ -29283,7 +29381,7 @@
         <v>2109</v>
       </c>
       <c r="I87" s="6" t="s">
-        <v>2113</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="88" spans="1:9" ht="13.5">
@@ -29312,7 +29410,7 @@
         <v>2109</v>
       </c>
       <c r="I88" s="6" t="s">
-        <v>2113</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="89" spans="1:9" ht="13.5">
@@ -29341,7 +29439,7 @@
         <v>2109</v>
       </c>
       <c r="I89" s="6" t="s">
-        <v>2113</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="90" spans="1:9" ht="13.5">
@@ -29370,7 +29468,7 @@
         <v>2109</v>
       </c>
       <c r="I90" s="6" t="s">
-        <v>2113</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="91" spans="1:9" ht="13.5">
@@ -29399,7 +29497,7 @@
         <v>2109</v>
       </c>
       <c r="I91" s="6" t="s">
-        <v>2113</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="92" spans="1:9" ht="13.5">
@@ -29428,7 +29526,7 @@
         <v>2109</v>
       </c>
       <c r="I92" s="6" t="s">
-        <v>2113</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="93" spans="1:9" ht="13.5">
@@ -29457,7 +29555,7 @@
         <v>2109</v>
       </c>
       <c r="I93" s="6" t="s">
-        <v>2113</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="94" spans="1:9" ht="13.5">
@@ -29486,7 +29584,7 @@
         <v>2109</v>
       </c>
       <c r="I94" s="6" t="s">
-        <v>2113</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="95" spans="1:9" ht="13.5">
@@ -29515,7 +29613,7 @@
         <v>2109</v>
       </c>
       <c r="I95" s="6" t="s">
-        <v>2113</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="96" spans="1:9" ht="13.5">
@@ -29544,7 +29642,7 @@
         <v>2109</v>
       </c>
       <c r="I96" s="6" t="s">
-        <v>2113</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="97" spans="1:9" ht="13.5">
@@ -29573,7 +29671,7 @@
         <v>2109</v>
       </c>
       <c r="I97" s="6" t="s">
-        <v>2113</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="98" spans="1:9" ht="13.5">
@@ -29602,7 +29700,7 @@
         <v>2109</v>
       </c>
       <c r="I98" s="6" t="s">
-        <v>2113</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="99" spans="1:9" ht="13.5">
@@ -29631,7 +29729,7 @@
         <v>2109</v>
       </c>
       <c r="I99" s="6" t="s">
-        <v>2113</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="100" spans="1:9" ht="13.5">
@@ -29660,7 +29758,7 @@
         <v>2109</v>
       </c>
       <c r="I100" s="6" t="s">
-        <v>2113</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="101" spans="1:9" ht="13.5">
@@ -29689,7 +29787,7 @@
         <v>2109</v>
       </c>
       <c r="I101" s="6" t="s">
-        <v>2113</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="102" spans="1:9" ht="13.5">
@@ -29718,7 +29816,7 @@
         <v>2109</v>
       </c>
       <c r="I102" s="6" t="s">
-        <v>2113</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="103" spans="1:9" ht="13.5">
@@ -29747,7 +29845,7 @@
         <v>2109</v>
       </c>
       <c r="I103" s="6" t="s">
-        <v>2113</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="104" spans="1:9" ht="13.5">
@@ -29776,7 +29874,7 @@
         <v>2109</v>
       </c>
       <c r="I104" s="6" t="s">
-        <v>2113</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="105" spans="1:9" ht="13.5">
@@ -29805,7 +29903,7 @@
         <v>2109</v>
       </c>
       <c r="I105" s="6" t="s">
-        <v>2113</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="106" spans="1:9" ht="13.5">
@@ -29834,7 +29932,7 @@
         <v>2109</v>
       </c>
       <c r="I106" s="6" t="s">
-        <v>2113</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="107" spans="1:9" ht="13.5">
@@ -29863,7 +29961,7 @@
         <v>2109</v>
       </c>
       <c r="I107" s="6" t="s">
-        <v>2113</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="108" spans="1:9" ht="13.5">
@@ -29892,7 +29990,7 @@
         <v>2109</v>
       </c>
       <c r="I108" s="6" t="s">
-        <v>2113</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="109" spans="1:9" ht="13.5">
@@ -29921,7 +30019,7 @@
         <v>2109</v>
       </c>
       <c r="I109" s="6" t="s">
-        <v>2113</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="110" spans="1:9" ht="13.5">
@@ -29950,7 +30048,7 @@
         <v>2109</v>
       </c>
       <c r="I110" s="6" t="s">
-        <v>2113</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="111" spans="1:9" ht="13.5">
@@ -29979,7 +30077,7 @@
         <v>2109</v>
       </c>
       <c r="I111" s="6" t="s">
-        <v>2113</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="112" spans="1:9" ht="13.5">
@@ -30008,7 +30106,7 @@
         <v>2109</v>
       </c>
       <c r="I112" s="6" t="s">
-        <v>2113</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="113" spans="1:9" ht="13.5">
@@ -30037,7 +30135,7 @@
         <v>2109</v>
       </c>
       <c r="I113" s="6" t="s">
-        <v>2113</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="114" spans="1:9" ht="13.5">
@@ -30066,7 +30164,7 @@
         <v>2109</v>
       </c>
       <c r="I114" s="6" t="s">
-        <v>2113</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="115" spans="1:9" ht="13.5">
@@ -30095,7 +30193,7 @@
         <v>2109</v>
       </c>
       <c r="I115" s="6" t="s">
-        <v>2113</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="116" spans="1:9" ht="13.5">
@@ -30124,7 +30222,7 @@
         <v>2109</v>
       </c>
       <c r="I116" s="6" t="s">
-        <v>2113</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="117" spans="1:9" ht="13.5">
@@ -30153,7 +30251,7 @@
         <v>2109</v>
       </c>
       <c r="I117" s="6" t="s">
-        <v>2113</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="118" spans="1:9" ht="13.5">
@@ -30182,7 +30280,7 @@
         <v>2109</v>
       </c>
       <c r="I118" s="6" t="s">
-        <v>2113</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="119" spans="1:9" ht="13.5">
@@ -30211,7 +30309,7 @@
         <v>2109</v>
       </c>
       <c r="I119" s="6" t="s">
-        <v>2113</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="120" spans="1:9" ht="13.5">
@@ -30240,7 +30338,7 @@
         <v>2109</v>
       </c>
       <c r="I120" s="6" t="s">
-        <v>2113</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="121" spans="1:9" ht="13.5">
@@ -30269,7 +30367,7 @@
         <v>2109</v>
       </c>
       <c r="I121" s="6" t="s">
-        <v>2113</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="122" spans="1:9" ht="13.5">
@@ -30298,7 +30396,7 @@
         <v>2109</v>
       </c>
       <c r="I122" s="6" t="s">
-        <v>2113</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="123" spans="1:9" ht="13.5">
@@ -30327,7 +30425,7 @@
         <v>2109</v>
       </c>
       <c r="I123" s="6" t="s">
-        <v>2113</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="124" spans="1:9" ht="13.5">
@@ -30356,7 +30454,7 @@
         <v>2109</v>
       </c>
       <c r="I124" s="6" t="s">
-        <v>2113</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="125" spans="1:9" ht="13.5">
@@ -30385,7 +30483,7 @@
         <v>2109</v>
       </c>
       <c r="I125" s="6" t="s">
-        <v>2113</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="126" spans="1:9" ht="13.5">
@@ -30414,7 +30512,7 @@
         <v>2109</v>
       </c>
       <c r="I126" s="6" t="s">
-        <v>2113</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="127" spans="1:9" ht="13.5">
@@ -30443,7 +30541,7 @@
         <v>2109</v>
       </c>
       <c r="I127" s="6" t="s">
-        <v>2113</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="128" spans="1:9" ht="13.5">
@@ -30472,7 +30570,7 @@
         <v>2109</v>
       </c>
       <c r="I128" s="6" t="s">
-        <v>2113</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="129" spans="1:9" ht="13.5">
@@ -30501,7 +30599,7 @@
         <v>2109</v>
       </c>
       <c r="I129" s="6" t="s">
-        <v>2113</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="130" spans="1:9" ht="13.5">
@@ -30530,7 +30628,7 @@
         <v>2109</v>
       </c>
       <c r="I130" s="6" t="s">
-        <v>2113</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="131" spans="1:9" ht="13.5">
@@ -30559,7 +30657,7 @@
         <v>2109</v>
       </c>
       <c r="I131" s="6" t="s">
-        <v>2113</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="132" spans="1:9" ht="13.5">
@@ -30588,7 +30686,7 @@
         <v>2109</v>
       </c>
       <c r="I132" s="6" t="s">
-        <v>2113</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="133" spans="1:9" ht="13.5">
@@ -30617,7 +30715,7 @@
         <v>2109</v>
       </c>
       <c r="I133" s="6" t="s">
-        <v>2113</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="134" spans="1:9" ht="13.5">
@@ -30646,7 +30744,7 @@
         <v>2109</v>
       </c>
       <c r="I134" s="6" t="s">
-        <v>2113</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="135" spans="1:9" ht="13.5">
@@ -30675,7 +30773,7 @@
         <v>2109</v>
       </c>
       <c r="I135" s="6" t="s">
-        <v>2113</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="136" spans="1:9" ht="13.5">
@@ -30704,7 +30802,7 @@
         <v>2109</v>
       </c>
       <c r="I136" s="6" t="s">
-        <v>2113</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="137" spans="1:9" ht="13.5">
@@ -30733,7 +30831,7 @@
         <v>2109</v>
       </c>
       <c r="I137" s="6" t="s">
-        <v>2114</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="138" spans="1:9" ht="13.5">
@@ -30762,7 +30860,7 @@
         <v>2109</v>
       </c>
       <c r="I138" s="6" t="s">
-        <v>2114</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="139" spans="1:9" ht="13.5">
@@ -30791,7 +30889,7 @@
         <v>2109</v>
       </c>
       <c r="I139" s="6" t="s">
-        <v>2114</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="140" spans="1:9" ht="13.5">
@@ -30820,7 +30918,7 @@
         <v>2109</v>
       </c>
       <c r="I140" s="6" t="s">
-        <v>2114</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="141" spans="1:9" ht="13.5">
@@ -30849,7 +30947,7 @@
         <v>2109</v>
       </c>
       <c r="I141" s="6" t="s">
-        <v>2114</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="142" spans="1:9" ht="13.5">
@@ -30878,7 +30976,7 @@
         <v>2109</v>
       </c>
       <c r="I142" s="6" t="s">
-        <v>2114</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="143" spans="1:9" ht="13.5">
@@ -30907,7 +31005,7 @@
         <v>2109</v>
       </c>
       <c r="I143" s="6" t="s">
-        <v>2114</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="144" spans="1:9" ht="13.5">
@@ -30936,7 +31034,7 @@
         <v>2109</v>
       </c>
       <c r="I144" s="6" t="s">
-        <v>2114</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="145" spans="1:9" ht="13.5">
@@ -30965,7 +31063,7 @@
         <v>2109</v>
       </c>
       <c r="I145" s="6" t="s">
-        <v>2114</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="146" spans="1:9" ht="13.5">
@@ -30994,7 +31092,7 @@
         <v>2109</v>
       </c>
       <c r="I146" s="6" t="s">
-        <v>2114</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="147" spans="1:9" ht="13.5">
@@ -31023,7 +31121,7 @@
         <v>2109</v>
       </c>
       <c r="I147" s="6" t="s">
-        <v>2114</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="148" spans="1:9" ht="13.5">
@@ -31052,7 +31150,7 @@
         <v>2109</v>
       </c>
       <c r="I148" s="6" t="s">
-        <v>2114</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="149" spans="1:9" ht="13.5">
@@ -31081,7 +31179,7 @@
         <v>2109</v>
       </c>
       <c r="I149" s="6" t="s">
-        <v>2114</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="150" spans="1:9" ht="13.5">
@@ -31110,7 +31208,7 @@
         <v>2109</v>
       </c>
       <c r="I150" s="6" t="s">
-        <v>2114</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="151" spans="1:9" ht="13.5">
@@ -31139,7 +31237,7 @@
         <v>2109</v>
       </c>
       <c r="I151" s="6" t="s">
-        <v>2114</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="152" spans="1:9" ht="13.5">
@@ -31168,7 +31266,7 @@
         <v>2109</v>
       </c>
       <c r="I152" s="6" t="s">
-        <v>2114</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="153" spans="1:9" ht="13.5">
@@ -31197,7 +31295,7 @@
         <v>2109</v>
       </c>
       <c r="I153" s="6" t="s">
-        <v>2114</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="154" spans="1:9" ht="13.5">
@@ -31226,7 +31324,7 @@
         <v>2109</v>
       </c>
       <c r="I154" s="6" t="s">
-        <v>2114</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="155" spans="1:9" ht="13.5">
@@ -31255,7 +31353,7 @@
         <v>2109</v>
       </c>
       <c r="I155" s="6" t="s">
-        <v>2114</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="156" spans="1:9" ht="13.5">
@@ -31284,7 +31382,7 @@
         <v>2109</v>
       </c>
       <c r="I156" s="6" t="s">
-        <v>2114</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="157" spans="1:9" ht="13.5">
@@ -31313,7 +31411,7 @@
         <v>2109</v>
       </c>
       <c r="I157" s="6" t="s">
-        <v>2114</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="158" spans="1:9" ht="13.5">
@@ -31342,7 +31440,7 @@
         <v>2109</v>
       </c>
       <c r="I158" s="6" t="s">
-        <v>2114</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="159" spans="1:9" ht="13.5">
@@ -31371,7 +31469,7 @@
         <v>2109</v>
       </c>
       <c r="I159" s="6" t="s">
-        <v>2114</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="160" spans="1:9" ht="13.5">
@@ -31400,7 +31498,7 @@
         <v>2109</v>
       </c>
       <c r="I160" s="6" t="s">
-        <v>2114</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="161" spans="1:9" ht="13.5">
@@ -31429,7 +31527,7 @@
         <v>2109</v>
       </c>
       <c r="I161" s="6" t="s">
-        <v>2114</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="162" spans="1:9" ht="13.5">
@@ -31458,7 +31556,7 @@
         <v>2109</v>
       </c>
       <c r="I162" s="6" t="s">
-        <v>2114</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="163" spans="1:9" ht="13.5">
@@ -31487,7 +31585,7 @@
         <v>2109</v>
       </c>
       <c r="I163" s="6" t="s">
-        <v>2114</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="164" spans="1:9" ht="13.5">
@@ -31516,7 +31614,7 @@
         <v>2109</v>
       </c>
       <c r="I164" s="6" t="s">
-        <v>2114</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="165" spans="1:9" ht="13.5">
@@ -31545,7 +31643,7 @@
         <v>2109</v>
       </c>
       <c r="I165" s="6" t="s">
-        <v>2114</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="166" spans="1:9" ht="13.5">
@@ -31574,7 +31672,7 @@
         <v>2109</v>
       </c>
       <c r="I166" s="6" t="s">
-        <v>2114</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="167" spans="1:9" ht="13.5">
@@ -31603,7 +31701,7 @@
         <v>2109</v>
       </c>
       <c r="I167" s="6" t="s">
-        <v>2114</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="168" spans="1:9" ht="13.5">
@@ -31632,7 +31730,7 @@
         <v>2109</v>
       </c>
       <c r="I168" s="6" t="s">
-        <v>2114</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="169" spans="1:9" ht="13.5">
@@ -31661,7 +31759,7 @@
         <v>2109</v>
       </c>
       <c r="I169" s="6" t="s">
-        <v>2114</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="170" spans="1:9" ht="13.5">
@@ -31690,7 +31788,7 @@
         <v>2109</v>
       </c>
       <c r="I170" s="6" t="s">
-        <v>2114</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="171" spans="1:9" ht="13.5">
@@ -31719,7 +31817,7 @@
         <v>2109</v>
       </c>
       <c r="I171" s="6" t="s">
-        <v>2114</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="172" spans="1:9" ht="13.5">
@@ -31748,7 +31846,7 @@
         <v>2109</v>
       </c>
       <c r="I172" s="6" t="s">
-        <v>2114</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="173" spans="1:9" ht="13.5">
@@ -31777,7 +31875,7 @@
         <v>2109</v>
       </c>
       <c r="I173" s="6" t="s">
-        <v>2114</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="174" spans="1:9" ht="13.5">
@@ -31806,7 +31904,7 @@
         <v>2109</v>
       </c>
       <c r="I174" s="6" t="s">
-        <v>2114</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="175" spans="1:9" ht="13.5">
@@ -31835,7 +31933,7 @@
         <v>2109</v>
       </c>
       <c r="I175" s="6" t="s">
-        <v>2114</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="176" spans="1:9" ht="13.5">
@@ -31864,7 +31962,7 @@
         <v>2109</v>
       </c>
       <c r="I176" s="6" t="s">
-        <v>2114</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="177" spans="1:9" ht="13.5">
@@ -31893,7 +31991,7 @@
         <v>2109</v>
       </c>
       <c r="I177" s="6" t="s">
-        <v>2114</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="178" spans="1:9" ht="13.5">
@@ -31922,7 +32020,7 @@
         <v>2109</v>
       </c>
       <c r="I178" s="6" t="s">
-        <v>2114</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="179" spans="1:9" ht="13.5">
@@ -31951,7 +32049,7 @@
         <v>2109</v>
       </c>
       <c r="I179" s="6" t="s">
-        <v>2114</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="180" spans="1:9" ht="13.5">
@@ -31980,7 +32078,7 @@
         <v>2109</v>
       </c>
       <c r="I180" s="6" t="s">
-        <v>2114</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="181" spans="1:9" ht="13.5">
@@ -32009,7 +32107,7 @@
         <v>2109</v>
       </c>
       <c r="I181" s="6" t="s">
-        <v>2114</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="182" spans="1:9" ht="13.5">
@@ -32038,7 +32136,7 @@
         <v>2109</v>
       </c>
       <c r="I182" s="6" t="s">
-        <v>2114</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="183" spans="1:9" ht="13.5">
@@ -32067,7 +32165,7 @@
         <v>2109</v>
       </c>
       <c r="I183" s="6" t="s">
-        <v>2114</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="184" spans="1:9" ht="13.5">
@@ -32096,7 +32194,7 @@
         <v>2109</v>
       </c>
       <c r="I184" s="6" t="s">
-        <v>2114</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="185" spans="1:9" ht="13.5">
@@ -32125,7 +32223,7 @@
         <v>2109</v>
       </c>
       <c r="I185" s="6" t="s">
-        <v>2114</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="186" spans="1:9" ht="13.5">
@@ -32154,7 +32252,7 @@
         <v>2109</v>
       </c>
       <c r="I186" s="6" t="s">
-        <v>2114</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="187" spans="1:9" ht="13.5">
@@ -32183,7 +32281,7 @@
         <v>2109</v>
       </c>
       <c r="I187" s="6" t="s">
-        <v>2114</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="188" spans="1:9" ht="13.5">
@@ -32212,7 +32310,7 @@
         <v>2109</v>
       </c>
       <c r="I188" s="6" t="s">
-        <v>2114</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="189" spans="1:9" ht="13.5">
@@ -32241,7 +32339,7 @@
         <v>2109</v>
       </c>
       <c r="I189" s="6" t="s">
-        <v>2114</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="190" spans="1:9" ht="13.5">
@@ -32270,7 +32368,7 @@
         <v>2109</v>
       </c>
       <c r="I190" s="6" t="s">
-        <v>2114</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="191" spans="1:9" ht="13.5">
@@ -32299,7 +32397,7 @@
         <v>2109</v>
       </c>
       <c r="I191" s="6" t="s">
-        <v>2114</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="192" spans="1:9" ht="13.5">
@@ -32328,7 +32426,7 @@
         <v>2109</v>
       </c>
       <c r="I192" s="6" t="s">
-        <v>2114</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="193" spans="1:10" ht="13.5">
@@ -32357,7 +32455,7 @@
         <v>2109</v>
       </c>
       <c r="I193" s="6" t="s">
-        <v>2114</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="194" spans="1:10" ht="13.5">
@@ -32386,7 +32484,7 @@
         <v>2109</v>
       </c>
       <c r="I194" s="6" t="s">
-        <v>2114</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="195" spans="1:10" ht="13.5">
@@ -32415,7 +32513,7 @@
         <v>2109</v>
       </c>
       <c r="I195" s="6" t="s">
-        <v>2114</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="196" spans="1:10" ht="13.5">
@@ -32444,7 +32542,7 @@
         <v>2109</v>
       </c>
       <c r="I196" s="6" t="s">
-        <v>2114</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="197" spans="1:10" ht="13.5">
@@ -32473,7 +32571,7 @@
         <v>2109</v>
       </c>
       <c r="I197" s="6" t="s">
-        <v>2114</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="198" spans="1:10" ht="13.5">
@@ -32502,7 +32600,7 @@
         <v>2109</v>
       </c>
       <c r="I198" s="6" t="s">
-        <v>2114</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="199" spans="1:10" ht="13.5">
@@ -32531,7 +32629,7 @@
         <v>2109</v>
       </c>
       <c r="I199" s="6" t="s">
-        <v>2114</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="200" spans="1:10" ht="13.5">
@@ -32560,7 +32658,7 @@
         <v>2109</v>
       </c>
       <c r="I200" s="6" t="s">
-        <v>2114</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="201" spans="1:10" ht="13.5">
@@ -32589,7 +32687,7 @@
         <v>2109</v>
       </c>
       <c r="I201" s="6" t="s">
-        <v>2114</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="202" spans="1:10" ht="13.5">
@@ -32618,7 +32716,7 @@
         <v>2109</v>
       </c>
       <c r="I202" s="6" t="s">
-        <v>2114</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="203" spans="1:10" ht="13.5">
@@ -32647,7 +32745,7 @@
         <v>2109</v>
       </c>
       <c r="I203" s="6" t="s">
-        <v>2114</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="204" spans="1:10" ht="13.5">
@@ -32676,7 +32774,7 @@
         <v>2109</v>
       </c>
       <c r="I204" s="6" t="s">
-        <v>2114</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="205" spans="1:10" ht="13.5">
@@ -32705,7 +32803,7 @@
         <v>2109</v>
       </c>
       <c r="I205" s="6" t="s">
-        <v>2114</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="206" spans="1:10" ht="13.5">
@@ -32735,7 +32833,7 @@
       </c>
       <c r="I206" s="6"/>
       <c r="J206" t="s">
-        <v>2115</v>
+        <v>2114</v>
       </c>
     </row>
     <row r="207" spans="1:10" ht="13.5">
@@ -32765,7 +32863,7 @@
       </c>
       <c r="I207" s="6"/>
       <c r="J207" t="s">
-        <v>2115</v>
+        <v>2114</v>
       </c>
     </row>
     <row r="208" spans="1:10" ht="13.5">
@@ -32794,7 +32892,7 @@
         <v>2109</v>
       </c>
       <c r="I208" s="6" t="s">
-        <v>2114</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="209" spans="1:10" ht="13.5">
@@ -32824,7 +32922,7 @@
       </c>
       <c r="I209" s="6"/>
       <c r="J209" t="s">
-        <v>2115</v>
+        <v>2114</v>
       </c>
     </row>
     <row r="210" spans="1:10" ht="13.5">
@@ -32853,7 +32951,7 @@
         <v>2109</v>
       </c>
       <c r="I210" s="6" t="s">
-        <v>2114</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="211" spans="1:10" ht="13.5">
@@ -32882,7 +32980,7 @@
         <v>2109</v>
       </c>
       <c r="I211" s="6" t="s">
-        <v>2114</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="212" spans="1:10" ht="13.5">
@@ -32911,7 +33009,7 @@
         <v>2109</v>
       </c>
       <c r="I212" s="6" t="s">
-        <v>2114</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="213" spans="1:10" ht="13.5">
@@ -32940,7 +33038,7 @@
         <v>2109</v>
       </c>
       <c r="I213" s="6" t="s">
-        <v>2114</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="214" spans="1:10" ht="13.5">
@@ -32969,7 +33067,7 @@
         <v>2109</v>
       </c>
       <c r="I214" s="6" t="s">
-        <v>2114</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="215" spans="1:10" ht="13.5">
@@ -32998,7 +33096,7 @@
         <v>2109</v>
       </c>
       <c r="I215" s="6" t="s">
-        <v>2114</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="216" spans="1:10" ht="13.5">
@@ -33027,7 +33125,7 @@
         <v>2109</v>
       </c>
       <c r="I216" s="6" t="s">
-        <v>2114</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="217" spans="1:10" ht="13.5">
@@ -33056,7 +33154,7 @@
         <v>2109</v>
       </c>
       <c r="I217" s="6" t="s">
-        <v>2114</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="218" spans="1:10" ht="13.5">
@@ -33085,7 +33183,7 @@
         <v>2109</v>
       </c>
       <c r="I218" s="6" t="s">
-        <v>2114</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="219" spans="1:10" ht="13.5">
@@ -33114,7 +33212,7 @@
         <v>2109</v>
       </c>
       <c r="I219" s="6" t="s">
-        <v>2114</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="220" spans="1:10" ht="13.5">
@@ -33143,7 +33241,7 @@
         <v>2109</v>
       </c>
       <c r="I220" s="6" t="s">
-        <v>2114</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="221" spans="1:10" ht="13.5">
@@ -33172,7 +33270,7 @@
         <v>2109</v>
       </c>
       <c r="I221" s="6" t="s">
-        <v>2114</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="222" spans="1:10" ht="13.5">
@@ -33201,7 +33299,7 @@
         <v>2109</v>
       </c>
       <c r="I222" s="6" t="s">
-        <v>2114</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="223" spans="1:10" ht="13.5">
@@ -33230,7 +33328,7 @@
         <v>2109</v>
       </c>
       <c r="I223" s="6" t="s">
-        <v>2114</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="224" spans="1:10" ht="13.5">
@@ -33259,10 +33357,10 @@
         <v>2109</v>
       </c>
       <c r="I224" s="6" t="s">
-        <v>2114</v>
-      </c>
-    </row>
-    <row r="225" spans="1:10" ht="13.5">
+        <v>2113</v>
+      </c>
+    </row>
+    <row r="225" spans="1:9" ht="13.5">
       <c r="A225" t="s">
         <v>44</v>
       </c>
@@ -33288,10 +33386,10 @@
         <v>2109</v>
       </c>
       <c r="I225" s="6" t="s">
-        <v>2114</v>
-      </c>
-    </row>
-    <row r="226" spans="1:10" ht="13.5">
+        <v>2113</v>
+      </c>
+    </row>
+    <row r="226" spans="1:9" ht="13.5">
       <c r="A226" t="s">
         <v>44</v>
       </c>
@@ -33317,10 +33415,10 @@
         <v>2109</v>
       </c>
       <c r="I226" s="6" t="s">
-        <v>2114</v>
-      </c>
-    </row>
-    <row r="227" spans="1:10" ht="13.5">
+        <v>2113</v>
+      </c>
+    </row>
+    <row r="227" spans="1:9" ht="13.5">
       <c r="A227" t="s">
         <v>44</v>
       </c>
@@ -33346,10 +33444,10 @@
         <v>2109</v>
       </c>
       <c r="I227" s="6" t="s">
-        <v>2114</v>
-      </c>
-    </row>
-    <row r="228" spans="1:10" ht="13.5">
+        <v>2113</v>
+      </c>
+    </row>
+    <row r="228" spans="1:9" ht="13.5">
       <c r="A228" t="s">
         <v>44</v>
       </c>
@@ -33375,10 +33473,10 @@
         <v>2109</v>
       </c>
       <c r="I228" s="6" t="s">
-        <v>2114</v>
-      </c>
-    </row>
-    <row r="229" spans="1:10" ht="13.5">
+        <v>2113</v>
+      </c>
+    </row>
+    <row r="229" spans="1:9" ht="13.5">
       <c r="A229" t="s">
         <v>44</v>
       </c>
@@ -33404,10 +33502,10 @@
         <v>2109</v>
       </c>
       <c r="I229" s="6" t="s">
-        <v>2114</v>
-      </c>
-    </row>
-    <row r="230" spans="1:10" ht="13.5">
+        <v>2113</v>
+      </c>
+    </row>
+    <row r="230" spans="1:9" ht="13.5">
       <c r="A230" t="s">
         <v>44</v>
       </c>
@@ -33433,10 +33531,10 @@
         <v>2109</v>
       </c>
       <c r="I230" s="6" t="s">
-        <v>2114</v>
-      </c>
-    </row>
-    <row r="231" spans="1:10" ht="13.5">
+        <v>2113</v>
+      </c>
+    </row>
+    <row r="231" spans="1:9" ht="13.5">
       <c r="A231" t="s">
         <v>44</v>
       </c>
@@ -33462,10 +33560,10 @@
         <v>2109</v>
       </c>
       <c r="I231" s="6" t="s">
-        <v>2114</v>
-      </c>
-    </row>
-    <row r="232" spans="1:10" ht="13.5">
+        <v>2113</v>
+      </c>
+    </row>
+    <row r="232" spans="1:9" ht="13.5">
       <c r="A232" t="s">
         <v>44</v>
       </c>
@@ -33491,10 +33589,10 @@
         <v>2109</v>
       </c>
       <c r="I232" s="6" t="s">
-        <v>2114</v>
-      </c>
-    </row>
-    <row r="233" spans="1:10" ht="13.5">
+        <v>2113</v>
+      </c>
+    </row>
+    <row r="233" spans="1:9" ht="13.5">
       <c r="A233" t="s">
         <v>44</v>
       </c>
@@ -33520,10 +33618,10 @@
         <v>2109</v>
       </c>
       <c r="I233" s="6" t="s">
-        <v>2114</v>
-      </c>
-    </row>
-    <row r="234" spans="1:10" ht="13.5">
+        <v>2113</v>
+      </c>
+    </row>
+    <row r="234" spans="1:9" ht="13.5">
       <c r="A234" t="s">
         <v>44</v>
       </c>
@@ -33549,10 +33647,10 @@
         <v>2109</v>
       </c>
       <c r="I234" s="6" t="s">
-        <v>2114</v>
-      </c>
-    </row>
-    <row r="235" spans="1:10" ht="13.5">
+        <v>2113</v>
+      </c>
+    </row>
+    <row r="235" spans="1:9" ht="13.5">
       <c r="A235" t="s">
         <v>44</v>
       </c>
@@ -33578,10 +33676,10 @@
         <v>2109</v>
       </c>
       <c r="I235" s="6" t="s">
-        <v>2114</v>
-      </c>
-    </row>
-    <row r="236" spans="1:10" ht="13.5">
+        <v>2113</v>
+      </c>
+    </row>
+    <row r="236" spans="1:9" ht="13.5">
       <c r="A236" t="s">
         <v>44</v>
       </c>
@@ -33607,10 +33705,10 @@
         <v>2109</v>
       </c>
       <c r="I236" s="6" t="s">
-        <v>2114</v>
-      </c>
-    </row>
-    <row r="237" spans="1:10" ht="13.5">
+        <v>2113</v>
+      </c>
+    </row>
+    <row r="237" spans="1:9" ht="13.5">
       <c r="A237" t="s">
         <v>44</v>
       </c>
@@ -33636,10 +33734,10 @@
         <v>2109</v>
       </c>
       <c r="I237" s="6" t="s">
-        <v>2114</v>
-      </c>
-    </row>
-    <row r="238" spans="1:10" ht="13.5">
+        <v>2113</v>
+      </c>
+    </row>
+    <row r="238" spans="1:9" ht="13.5">
       <c r="A238" t="s">
         <v>44</v>
       </c>
@@ -33659,17 +33757,16 @@
         <v>1</v>
       </c>
       <c r="G238" s="6" t="s">
-        <v>1590</v>
+        <v>1606</v>
       </c>
       <c r="H238" s="6" t="s">
         <v>2109</v>
       </c>
-      <c r="I238" s="6"/>
-      <c r="J238" t="s">
-        <v>2115</v>
-      </c>
-    </row>
-    <row r="239" spans="1:10" ht="13.5">
+      <c r="I238" s="6" t="s">
+        <v>2253</v>
+      </c>
+    </row>
+    <row r="239" spans="1:9" ht="13.5">
       <c r="A239" t="s">
         <v>44</v>
       </c>
@@ -33695,10 +33792,10 @@
         <v>2109</v>
       </c>
       <c r="I239" s="6" t="s">
-        <v>2114</v>
-      </c>
-    </row>
-    <row r="240" spans="1:10" ht="13.5">
+        <v>2113</v>
+      </c>
+    </row>
+    <row r="240" spans="1:9" ht="13.5">
       <c r="A240" t="s">
         <v>44</v>
       </c>
@@ -33724,7 +33821,7 @@
         <v>2109</v>
       </c>
       <c r="I240" s="6" t="s">
-        <v>2114</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="241" spans="1:9" ht="13.5">
@@ -33753,7 +33850,7 @@
         <v>2109</v>
       </c>
       <c r="I241" s="6" t="s">
-        <v>2114</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="242" spans="1:9" ht="13.5">
@@ -33782,7 +33879,7 @@
         <v>2109</v>
       </c>
       <c r="I242" s="6" t="s">
-        <v>2114</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="243" spans="1:9" ht="13.5">
@@ -33811,7 +33908,7 @@
         <v>2109</v>
       </c>
       <c r="I243" s="6" t="s">
-        <v>2114</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="244" spans="1:9" ht="13.5">
@@ -33840,7 +33937,7 @@
         <v>2109</v>
       </c>
       <c r="I244" s="6" t="s">
-        <v>2114</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="245" spans="1:9" ht="13.5">
@@ -33869,7 +33966,7 @@
         <v>2109</v>
       </c>
       <c r="I245" s="6" t="s">
-        <v>2114</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="246" spans="1:9" ht="13.5">
@@ -33892,12 +33989,14 @@
         <v>1</v>
       </c>
       <c r="G246" s="6" t="s">
-        <v>2108</v>
+        <v>1606</v>
       </c>
       <c r="H246" s="6" t="s">
         <v>2109</v>
       </c>
-      <c r="I246" s="6"/>
+      <c r="I246" s="6" t="s">
+        <v>2254</v>
+      </c>
     </row>
     <row r="247" spans="1:9" ht="13.5">
       <c r="A247" t="s">
@@ -33919,12 +34018,14 @@
         <v>1</v>
       </c>
       <c r="G247" s="6" t="s">
-        <v>2108</v>
+        <v>1606</v>
       </c>
       <c r="H247" s="6" t="s">
         <v>2109</v>
       </c>
-      <c r="I247" s="6"/>
+      <c r="I247" s="6" t="s">
+        <v>2254</v>
+      </c>
     </row>
     <row r="248" spans="1:9" ht="13.5">
       <c r="A248" t="s">
@@ -33946,12 +34047,14 @@
         <v>1</v>
       </c>
       <c r="G248" s="6" t="s">
-        <v>2108</v>
+        <v>1606</v>
       </c>
       <c r="H248" s="6" t="s">
         <v>2109</v>
       </c>
-      <c r="I248" s="6"/>
+      <c r="I248" s="6" t="s">
+        <v>2254</v>
+      </c>
     </row>
     <row r="249" spans="1:9" ht="13.5">
       <c r="A249" t="s">
@@ -33973,12 +34076,14 @@
         <v>1</v>
       </c>
       <c r="G249" s="6" t="s">
-        <v>2108</v>
+        <v>1606</v>
       </c>
       <c r="H249" s="6" t="s">
         <v>2109</v>
       </c>
-      <c r="I249" s="6"/>
+      <c r="I249" s="6" t="s">
+        <v>2254</v>
+      </c>
     </row>
     <row r="250" spans="1:9" ht="13.5">
       <c r="A250" t="s">
@@ -34000,12 +34105,14 @@
         <v>1</v>
       </c>
       <c r="G250" s="6" t="s">
-        <v>2108</v>
+        <v>1606</v>
       </c>
       <c r="H250" s="6" t="s">
         <v>2109</v>
       </c>
-      <c r="I250" s="6"/>
+      <c r="I250" s="6" t="s">
+        <v>2254</v>
+      </c>
     </row>
     <row r="251" spans="1:9" ht="13.5">
       <c r="A251" t="s">
@@ -34027,12 +34134,14 @@
         <v>1</v>
       </c>
       <c r="G251" s="6" t="s">
-        <v>2108</v>
+        <v>1606</v>
       </c>
       <c r="H251" s="6" t="s">
         <v>2109</v>
       </c>
-      <c r="I251" s="6"/>
+      <c r="I251" s="6" t="s">
+        <v>2254</v>
+      </c>
     </row>
     <row r="252" spans="1:9" ht="13.5">
       <c r="A252" t="s">
@@ -34054,12 +34163,14 @@
         <v>1</v>
       </c>
       <c r="G252" s="6" t="s">
-        <v>2108</v>
+        <v>1606</v>
       </c>
       <c r="H252" s="6" t="s">
         <v>2109</v>
       </c>
-      <c r="I252" s="6"/>
+      <c r="I252" s="6" t="s">
+        <v>2254</v>
+      </c>
     </row>
     <row r="253" spans="1:9" ht="13.5">
       <c r="A253" t="s">
@@ -34081,12 +34192,14 @@
         <v>1</v>
       </c>
       <c r="G253" s="6" t="s">
-        <v>2108</v>
+        <v>1606</v>
       </c>
       <c r="H253" s="6" t="s">
         <v>2109</v>
       </c>
-      <c r="I253" s="6"/>
+      <c r="I253" s="6" t="s">
+        <v>2254</v>
+      </c>
     </row>
     <row r="254" spans="1:9" ht="13.5">
       <c r="A254" t="s">
@@ -34108,12 +34221,14 @@
         <v>1</v>
       </c>
       <c r="G254" s="6" t="s">
-        <v>2108</v>
+        <v>1606</v>
       </c>
       <c r="H254" s="6" t="s">
         <v>2109</v>
       </c>
-      <c r="I254" s="6"/>
+      <c r="I254" s="6" t="s">
+        <v>2254</v>
+      </c>
     </row>
     <row r="255" spans="1:9" ht="13.5">
       <c r="A255" t="s">
@@ -34135,12 +34250,14 @@
         <v>1</v>
       </c>
       <c r="G255" s="6" t="s">
-        <v>2108</v>
+        <v>1606</v>
       </c>
       <c r="H255" s="6" t="s">
         <v>2109</v>
       </c>
-      <c r="I255" s="6"/>
+      <c r="I255" s="6" t="s">
+        <v>2254</v>
+      </c>
     </row>
     <row r="256" spans="1:9" ht="13.5">
       <c r="A256" t="s">
@@ -34162,12 +34279,14 @@
         <v>1</v>
       </c>
       <c r="G256" s="6" t="s">
-        <v>2108</v>
+        <v>1606</v>
       </c>
       <c r="H256" s="6" t="s">
         <v>2109</v>
       </c>
-      <c r="I256" s="6"/>
+      <c r="I256" s="6" t="s">
+        <v>2255</v>
+      </c>
     </row>
     <row r="257" spans="1:9" ht="13.5">
       <c r="A257" t="s">
@@ -34189,12 +34308,14 @@
         <v>1</v>
       </c>
       <c r="G257" s="6" t="s">
-        <v>2108</v>
+        <v>1606</v>
       </c>
       <c r="H257" s="6" t="s">
         <v>2109</v>
       </c>
-      <c r="I257" s="6"/>
+      <c r="I257" s="6" t="s">
+        <v>2255</v>
+      </c>
     </row>
     <row r="258" spans="1:9" ht="13.5">
       <c r="A258" t="s">
@@ -34216,12 +34337,14 @@
         <v>1</v>
       </c>
       <c r="G258" s="6" t="s">
-        <v>2108</v>
+        <v>1606</v>
       </c>
       <c r="H258" s="6" t="s">
         <v>2109</v>
       </c>
-      <c r="I258" s="6"/>
+      <c r="I258" s="6" t="s">
+        <v>2255</v>
+      </c>
     </row>
     <row r="259" spans="1:9" ht="13.5">
       <c r="A259" t="s">
@@ -34243,12 +34366,14 @@
         <v>1</v>
       </c>
       <c r="G259" s="6" t="s">
-        <v>2108</v>
+        <v>1606</v>
       </c>
       <c r="H259" s="6" t="s">
         <v>2109</v>
       </c>
-      <c r="I259" s="6"/>
+      <c r="I259" s="6" t="s">
+        <v>2255</v>
+      </c>
     </row>
     <row r="260" spans="1:9" ht="13.5">
       <c r="A260" t="s">
@@ -34270,12 +34395,14 @@
         <v>1</v>
       </c>
       <c r="G260" s="6" t="s">
-        <v>2108</v>
+        <v>1606</v>
       </c>
       <c r="H260" s="6" t="s">
         <v>2109</v>
       </c>
-      <c r="I260" s="6"/>
+      <c r="I260" s="6" t="s">
+        <v>2255</v>
+      </c>
     </row>
     <row r="261" spans="1:9" ht="13.5">
       <c r="A261" t="s">
@@ -34297,12 +34424,14 @@
         <v>1</v>
       </c>
       <c r="G261" s="6" t="s">
-        <v>2108</v>
+        <v>1606</v>
       </c>
       <c r="H261" s="6" t="s">
         <v>2109</v>
       </c>
-      <c r="I261" s="6"/>
+      <c r="I261" s="6" t="s">
+        <v>2255</v>
+      </c>
     </row>
     <row r="262" spans="1:9" ht="13.5">
       <c r="A262" t="s">
@@ -34324,12 +34453,14 @@
         <v>1</v>
       </c>
       <c r="G262" s="6" t="s">
-        <v>2108</v>
+        <v>1606</v>
       </c>
       <c r="H262" s="6" t="s">
         <v>2109</v>
       </c>
-      <c r="I262" s="6"/>
+      <c r="I262" s="6" t="s">
+        <v>2255</v>
+      </c>
     </row>
     <row r="263" spans="1:9" ht="13.5">
       <c r="A263" t="s">
@@ -34351,12 +34482,14 @@
         <v>1</v>
       </c>
       <c r="G263" s="6" t="s">
-        <v>2108</v>
+        <v>1606</v>
       </c>
       <c r="H263" s="6" t="s">
         <v>2109</v>
       </c>
-      <c r="I263" s="6"/>
+      <c r="I263" s="6" t="s">
+        <v>2255</v>
+      </c>
     </row>
     <row r="264" spans="1:9" ht="13.5">
       <c r="A264" t="s">
@@ -34378,12 +34511,14 @@
         <v>1</v>
       </c>
       <c r="G264" s="6" t="s">
-        <v>2108</v>
+        <v>1606</v>
       </c>
       <c r="H264" s="6" t="s">
         <v>2109</v>
       </c>
-      <c r="I264" s="6"/>
+      <c r="I264" s="6" t="s">
+        <v>2255</v>
+      </c>
     </row>
     <row r="265" spans="1:9" ht="13.5">
       <c r="A265" t="s">
@@ -34405,12 +34540,14 @@
         <v>1</v>
       </c>
       <c r="G265" s="6" t="s">
-        <v>2108</v>
+        <v>1606</v>
       </c>
       <c r="H265" s="6" t="s">
         <v>2109</v>
       </c>
-      <c r="I265" s="6"/>
+      <c r="I265" s="6" t="s">
+        <v>2255</v>
+      </c>
     </row>
     <row r="266" spans="1:9" ht="13.5">
       <c r="A266" t="s">
@@ -34432,12 +34569,14 @@
         <v>1</v>
       </c>
       <c r="G266" s="6" t="s">
-        <v>2108</v>
+        <v>1606</v>
       </c>
       <c r="H266" s="6" t="s">
         <v>2109</v>
       </c>
-      <c r="I266" s="6"/>
+      <c r="I266" s="6" t="s">
+        <v>2255</v>
+      </c>
     </row>
     <row r="267" spans="1:9" ht="13.5">
       <c r="A267" t="s">
@@ -34459,12 +34598,14 @@
         <v>1</v>
       </c>
       <c r="G267" s="6" t="s">
-        <v>2108</v>
+        <v>1606</v>
       </c>
       <c r="H267" s="6" t="s">
         <v>2109</v>
       </c>
-      <c r="I267" s="6"/>
+      <c r="I267" s="6" t="s">
+        <v>2255</v>
+      </c>
     </row>
     <row r="268" spans="1:9" ht="13.5">
       <c r="A268" t="s">
@@ -34486,12 +34627,14 @@
         <v>1</v>
       </c>
       <c r="G268" s="6" t="s">
-        <v>2108</v>
+        <v>1606</v>
       </c>
       <c r="H268" s="6" t="s">
         <v>2109</v>
       </c>
-      <c r="I268" s="6"/>
+      <c r="I268" s="6" t="s">
+        <v>2255</v>
+      </c>
     </row>
     <row r="269" spans="1:9" ht="13.5">
       <c r="A269" t="s">
@@ -34513,12 +34656,14 @@
         <v>1</v>
       </c>
       <c r="G269" s="6" t="s">
-        <v>2108</v>
+        <v>1606</v>
       </c>
       <c r="H269" s="6" t="s">
         <v>2109</v>
       </c>
-      <c r="I269" s="6"/>
+      <c r="I269" s="6" t="s">
+        <v>2255</v>
+      </c>
     </row>
     <row r="270" spans="1:9" ht="13.5">
       <c r="A270" t="s">
@@ -34540,12 +34685,14 @@
         <v>1</v>
       </c>
       <c r="G270" s="6" t="s">
-        <v>2108</v>
+        <v>1606</v>
       </c>
       <c r="H270" s="6" t="s">
         <v>2109</v>
       </c>
-      <c r="I270" s="6"/>
+      <c r="I270" s="6" t="s">
+        <v>2255</v>
+      </c>
     </row>
     <row r="271" spans="1:9" ht="13.5">
       <c r="A271" t="s">
@@ -34567,12 +34714,14 @@
         <v>1</v>
       </c>
       <c r="G271" s="6" t="s">
-        <v>2108</v>
+        <v>1606</v>
       </c>
       <c r="H271" s="6" t="s">
         <v>2109</v>
       </c>
-      <c r="I271" s="6"/>
+      <c r="I271" s="6" t="s">
+        <v>2255</v>
+      </c>
     </row>
     <row r="272" spans="1:9" ht="13.5">
       <c r="A272" t="s">
@@ -34594,12 +34743,14 @@
         <v>1</v>
       </c>
       <c r="G272" s="6" t="s">
-        <v>2108</v>
+        <v>1606</v>
       </c>
       <c r="H272" s="6" t="s">
         <v>2109</v>
       </c>
-      <c r="I272" s="6"/>
+      <c r="I272" s="6" t="s">
+        <v>2255</v>
+      </c>
     </row>
     <row r="273" spans="1:9" ht="13.5">
       <c r="A273" t="s">
@@ -34621,12 +34772,14 @@
         <v>1</v>
       </c>
       <c r="G273" s="6" t="s">
-        <v>2108</v>
+        <v>1606</v>
       </c>
       <c r="H273" s="6" t="s">
         <v>2109</v>
       </c>
-      <c r="I273" s="6"/>
+      <c r="I273" s="6" t="s">
+        <v>2255</v>
+      </c>
     </row>
     <row r="274" spans="1:9" ht="13.5">
       <c r="A274" t="s">
@@ -34648,12 +34801,14 @@
         <v>1</v>
       </c>
       <c r="G274" s="6" t="s">
-        <v>2108</v>
+        <v>1606</v>
       </c>
       <c r="H274" s="6" t="s">
         <v>2109</v>
       </c>
-      <c r="I274" s="6"/>
+      <c r="I274" s="6" t="s">
+        <v>2255</v>
+      </c>
     </row>
     <row r="275" spans="1:9" ht="13.5">
       <c r="A275" t="s">
@@ -34675,12 +34830,14 @@
         <v>1</v>
       </c>
       <c r="G275" s="6" t="s">
-        <v>2108</v>
+        <v>1606</v>
       </c>
       <c r="H275" s="6" t="s">
         <v>2109</v>
       </c>
-      <c r="I275" s="6"/>
+      <c r="I275" s="6" t="s">
+        <v>2255</v>
+      </c>
     </row>
     <row r="276" spans="1:9" ht="13.5">
       <c r="A276" t="s">
@@ -34702,12 +34859,14 @@
         <v>1</v>
       </c>
       <c r="G276" s="6" t="s">
-        <v>2108</v>
+        <v>1606</v>
       </c>
       <c r="H276" s="6" t="s">
         <v>2109</v>
       </c>
-      <c r="I276" s="6"/>
+      <c r="I276" s="6" t="s">
+        <v>2255</v>
+      </c>
     </row>
     <row r="277" spans="1:9" ht="13.5">
       <c r="A277" t="s">
@@ -34729,12 +34888,14 @@
         <v>1</v>
       </c>
       <c r="G277" s="6" t="s">
-        <v>2108</v>
+        <v>1606</v>
       </c>
       <c r="H277" s="6" t="s">
         <v>2109</v>
       </c>
-      <c r="I277" s="6"/>
+      <c r="I277" s="6" t="s">
+        <v>2255</v>
+      </c>
     </row>
     <row r="278" spans="1:9" ht="13.5">
       <c r="A278" t="s">
@@ -34756,12 +34917,14 @@
         <v>1</v>
       </c>
       <c r="G278" s="6" t="s">
-        <v>2108</v>
+        <v>1606</v>
       </c>
       <c r="H278" s="6" t="s">
         <v>2109</v>
       </c>
-      <c r="I278" s="6"/>
+      <c r="I278" s="6" t="s">
+        <v>2255</v>
+      </c>
     </row>
     <row r="279" spans="1:9" ht="13.5">
       <c r="A279" t="s">
@@ -34789,7 +34952,7 @@
         <v>2109</v>
       </c>
       <c r="I279" s="6" t="s">
-        <v>2252</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="280" spans="1:9" ht="13.5">
@@ -34818,7 +34981,7 @@
         <v>2109</v>
       </c>
       <c r="I280" s="6" t="s">
-        <v>2252</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="281" spans="1:9" ht="13.5">
@@ -34847,7 +35010,7 @@
         <v>2109</v>
       </c>
       <c r="I281" s="6" t="s">
-        <v>2252</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="282" spans="1:9" ht="13.5">
@@ -34876,7 +35039,7 @@
         <v>2109</v>
       </c>
       <c r="I282" s="6" t="s">
-        <v>2252</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="283" spans="1:9" ht="13.5">
@@ -34905,7 +35068,7 @@
         <v>2109</v>
       </c>
       <c r="I283" s="6" t="s">
-        <v>2252</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="284" spans="1:9" ht="13.5">
@@ -34934,7 +35097,7 @@
         <v>2109</v>
       </c>
       <c r="I284" s="6" t="s">
-        <v>2252</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="285" spans="1:9" ht="13.5">
@@ -34963,7 +35126,7 @@
         <v>2109</v>
       </c>
       <c r="I285" s="6" t="s">
-        <v>2252</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="286" spans="1:9" ht="13.5">
@@ -34992,7 +35155,7 @@
         <v>2109</v>
       </c>
       <c r="I286" s="6" t="s">
-        <v>2252</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="287" spans="1:9" ht="13.5">
@@ -35021,7 +35184,7 @@
         <v>2109</v>
       </c>
       <c r="I287" s="6" t="s">
-        <v>2252</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="288" spans="1:9" ht="13.5">
@@ -35050,7 +35213,7 @@
         <v>2109</v>
       </c>
       <c r="I288" s="6" t="s">
-        <v>2252</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="289" spans="1:9" ht="13.5">
@@ -35079,7 +35242,7 @@
         <v>2109</v>
       </c>
       <c r="I289" s="6" t="s">
-        <v>2252</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="290" spans="1:9" ht="13.5">
@@ -35108,7 +35271,7 @@
         <v>2109</v>
       </c>
       <c r="I290" s="6" t="s">
-        <v>2252</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="291" spans="1:9" ht="13.5">
@@ -35137,7 +35300,7 @@
         <v>2109</v>
       </c>
       <c r="I291" s="6" t="s">
-        <v>2252</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="292" spans="1:9" ht="13.5">
@@ -35166,7 +35329,7 @@
         <v>2109</v>
       </c>
       <c r="I292" s="6" t="s">
-        <v>2252</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="293" spans="1:9" ht="13.5">
@@ -35195,7 +35358,7 @@
         <v>2109</v>
       </c>
       <c r="I293" s="6" t="s">
-        <v>2252</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="294" spans="1:9" ht="13.5">
@@ -35224,7 +35387,7 @@
         <v>2109</v>
       </c>
       <c r="I294" s="6" t="s">
-        <v>2252</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="295" spans="1:9" ht="13.5">
@@ -35253,7 +35416,7 @@
         <v>2109</v>
       </c>
       <c r="I295" s="6" t="s">
-        <v>2252</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="296" spans="1:9" ht="13.5">
@@ -35282,7 +35445,7 @@
         <v>2109</v>
       </c>
       <c r="I296" s="6" t="s">
-        <v>2252</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="297" spans="1:9" ht="13.5">
@@ -35311,7 +35474,7 @@
         <v>2109</v>
       </c>
       <c r="I297" s="6" t="s">
-        <v>2252</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="298" spans="1:9" ht="13.5">
@@ -35340,7 +35503,7 @@
         <v>2109</v>
       </c>
       <c r="I298" s="6" t="s">
-        <v>2252</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="299" spans="1:9" ht="13.5">
@@ -35369,7 +35532,7 @@
         <v>2109</v>
       </c>
       <c r="I299" s="6" t="s">
-        <v>2252</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="300" spans="1:9" ht="13.5">
@@ -35398,7 +35561,7 @@
         <v>2109</v>
       </c>
       <c r="I300" s="6" t="s">
-        <v>2252</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="301" spans="1:9" ht="13.5">
@@ -35427,7 +35590,7 @@
         <v>2109</v>
       </c>
       <c r="I301" s="6" t="s">
-        <v>2252</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="302" spans="1:9" ht="13.5">
@@ -35456,7 +35619,7 @@
         <v>2109</v>
       </c>
       <c r="I302" s="6" t="s">
-        <v>2252</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="303" spans="1:9" ht="13.5">
@@ -35485,7 +35648,7 @@
         <v>2109</v>
       </c>
       <c r="I303" s="6" t="s">
-        <v>2252</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="304" spans="1:9" ht="13.5">
@@ -35514,7 +35677,7 @@
         <v>2109</v>
       </c>
       <c r="I304" s="6" t="s">
-        <v>2252</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="305" spans="1:9" ht="13.5">
@@ -35543,7 +35706,7 @@
         <v>2109</v>
       </c>
       <c r="I305" s="6" t="s">
-        <v>2252</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="306" spans="1:9" ht="13.5">
@@ -35566,12 +35729,14 @@
         <v>1</v>
       </c>
       <c r="G306" s="6" t="s">
-        <v>1590</v>
+        <v>1606</v>
       </c>
       <c r="H306" s="6" t="s">
         <v>2109</v>
       </c>
-      <c r="I306" s="6"/>
+      <c r="I306" s="6" t="s">
+        <v>2250</v>
+      </c>
     </row>
     <row r="307" spans="1:9" ht="13.5">
       <c r="A307" t="s">
@@ -35593,12 +35758,14 @@
         <v>1</v>
       </c>
       <c r="G307" s="6" t="s">
-        <v>1590</v>
+        <v>1606</v>
       </c>
       <c r="H307" s="6" t="s">
         <v>2109</v>
       </c>
-      <c r="I307" s="6"/>
+      <c r="I307" s="6" t="s">
+        <v>2250</v>
+      </c>
     </row>
     <row r="308" spans="1:9" ht="13.5">
       <c r="A308" t="s">
@@ -35626,7 +35793,7 @@
         <v>2109</v>
       </c>
       <c r="I308" s="6" t="s">
-        <v>2252</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="309" spans="1:9" ht="13.5">
@@ -35655,7 +35822,7 @@
         <v>2109</v>
       </c>
       <c r="I309" s="6" t="s">
-        <v>2252</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="310" spans="1:9" ht="13.5">
@@ -35684,7 +35851,7 @@
         <v>2109</v>
       </c>
       <c r="I310" s="6" t="s">
-        <v>2252</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="311" spans="1:9" ht="13.5">
@@ -35713,7 +35880,7 @@
         <v>2109</v>
       </c>
       <c r="I311" s="6" t="s">
-        <v>2252</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="312" spans="1:9" ht="13.5">
@@ -35742,7 +35909,7 @@
         <v>2109</v>
       </c>
       <c r="I312" s="6" t="s">
-        <v>2252</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="313" spans="1:9" ht="13.5">
@@ -35771,7 +35938,7 @@
         <v>2109</v>
       </c>
       <c r="I313" s="6" t="s">
-        <v>2252</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="314" spans="1:9" ht="13.5">
@@ -35800,7 +35967,7 @@
         <v>2109</v>
       </c>
       <c r="I314" s="6" t="s">
-        <v>2252</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="315" spans="1:9" ht="13.5">
@@ -35829,7 +35996,7 @@
         <v>2109</v>
       </c>
       <c r="I315" s="6" t="s">
-        <v>2252</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="316" spans="1:9" ht="13.5">
@@ -35858,7 +36025,7 @@
         <v>2109</v>
       </c>
       <c r="I316" s="6" t="s">
-        <v>2252</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="317" spans="1:9" ht="13.5">
@@ -35887,7 +36054,7 @@
         <v>2109</v>
       </c>
       <c r="I317" s="6" t="s">
-        <v>2252</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="318" spans="1:9" ht="13.5">
@@ -35916,7 +36083,7 @@
         <v>2109</v>
       </c>
       <c r="I318" s="6" t="s">
-        <v>2252</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="319" spans="1:9" ht="13.5">
@@ -35945,7 +36112,7 @@
         <v>2109</v>
       </c>
       <c r="I319" s="6" t="s">
-        <v>2252</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="320" spans="1:9" ht="13.5">
@@ -35974,7 +36141,7 @@
         <v>2109</v>
       </c>
       <c r="I320" s="6" t="s">
-        <v>2252</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="321" spans="1:9" ht="13.5">
@@ -36003,7 +36170,7 @@
         <v>2109</v>
       </c>
       <c r="I321" s="6" t="s">
-        <v>2252</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="322" spans="1:9" ht="13.5">
@@ -36032,7 +36199,7 @@
         <v>2109</v>
       </c>
       <c r="I322" s="6" t="s">
-        <v>2252</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="323" spans="1:9" ht="13.5">
@@ -36061,7 +36228,7 @@
         <v>2109</v>
       </c>
       <c r="I323" s="6" t="s">
-        <v>2252</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="324" spans="1:9" ht="13.5">
@@ -36090,7 +36257,7 @@
         <v>2109</v>
       </c>
       <c r="I324" s="6" t="s">
-        <v>2252</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="325" spans="1:9" ht="13.5">
@@ -36119,7 +36286,7 @@
         <v>2109</v>
       </c>
       <c r="I325" s="6" t="s">
-        <v>2252</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="326" spans="1:9" ht="13.5">
@@ -36148,7 +36315,7 @@
         <v>2109</v>
       </c>
       <c r="I326" s="6" t="s">
-        <v>2252</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="327" spans="1:9" ht="13.5">
@@ -36177,7 +36344,7 @@
         <v>2109</v>
       </c>
       <c r="I327" s="6" t="s">
-        <v>2252</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="328" spans="1:9" ht="13.5">
@@ -36206,7 +36373,7 @@
         <v>2109</v>
       </c>
       <c r="I328" s="6" t="s">
-        <v>2252</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="329" spans="1:9" ht="13.5">
@@ -36235,7 +36402,7 @@
         <v>2109</v>
       </c>
       <c r="I329" s="6" t="s">
-        <v>2252</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="330" spans="1:9" ht="13.5">
@@ -36264,7 +36431,7 @@
         <v>2109</v>
       </c>
       <c r="I330" s="6" t="s">
-        <v>2252</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="331" spans="1:9" ht="13.5">
@@ -36293,7 +36460,7 @@
         <v>2109</v>
       </c>
       <c r="I331" s="6" t="s">
-        <v>2252</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="332" spans="1:9" ht="13.5">
@@ -36322,7 +36489,7 @@
         <v>2109</v>
       </c>
       <c r="I332" s="6" t="s">
-        <v>2252</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="333" spans="1:9" ht="13.5">
@@ -36351,7 +36518,7 @@
         <v>2109</v>
       </c>
       <c r="I333" s="6" t="s">
-        <v>2252</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="334" spans="1:9" ht="13.5">
@@ -36380,7 +36547,7 @@
         <v>2109</v>
       </c>
       <c r="I334" s="6" t="s">
-        <v>2252</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="335" spans="1:9" ht="13.5">
@@ -36409,7 +36576,7 @@
         <v>2109</v>
       </c>
       <c r="I335" s="6" t="s">
-        <v>2252</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="336" spans="1:9" ht="13.5">
@@ -36438,7 +36605,7 @@
         <v>2109</v>
       </c>
       <c r="I336" s="6" t="s">
-        <v>2252</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="337" spans="1:9" ht="13.5">
@@ -36467,7 +36634,7 @@
         <v>2109</v>
       </c>
       <c r="I337" s="6" t="s">
-        <v>2252</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="338" spans="1:9" ht="13.5">
@@ -36496,7 +36663,7 @@
         <v>2109</v>
       </c>
       <c r="I338" s="6" t="s">
-        <v>2252</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="339" spans="1:9" ht="13.5">
@@ -36525,7 +36692,7 @@
         <v>2109</v>
       </c>
       <c r="I339" s="6" t="s">
-        <v>2252</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="340" spans="1:9" ht="13.5">
@@ -36554,7 +36721,7 @@
         <v>2109</v>
       </c>
       <c r="I340" s="6" t="s">
-        <v>2252</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="341" spans="1:9" ht="13.5">
@@ -36583,7 +36750,7 @@
         <v>2109</v>
       </c>
       <c r="I341" s="6" t="s">
-        <v>2252</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="342" spans="1:9" ht="13.5">
@@ -36612,7 +36779,7 @@
         <v>2109</v>
       </c>
       <c r="I342" s="6" t="s">
-        <v>2252</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="343" spans="1:9" ht="13.5">
@@ -36641,7 +36808,7 @@
         <v>2109</v>
       </c>
       <c r="I343" s="6" t="s">
-        <v>2252</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="344" spans="1:9" ht="13.5">
@@ -36670,7 +36837,7 @@
         <v>2109</v>
       </c>
       <c r="I344" s="6" t="s">
-        <v>2252</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="345" spans="1:9" ht="13.5">
@@ -36699,7 +36866,7 @@
         <v>2109</v>
       </c>
       <c r="I345" s="6" t="s">
-        <v>2252</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="346" spans="1:9" ht="13.5">
@@ -36728,7 +36895,7 @@
         <v>2109</v>
       </c>
       <c r="I346" s="6" t="s">
-        <v>2252</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="347" spans="1:9" ht="13.5">
@@ -36757,7 +36924,7 @@
         <v>2109</v>
       </c>
       <c r="I347" s="6" t="s">
-        <v>2252</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="348" spans="1:9" ht="13.5">
@@ -36786,7 +36953,7 @@
         <v>2109</v>
       </c>
       <c r="I348" s="6" t="s">
-        <v>2252</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="349" spans="1:9" ht="13.5">
@@ -36815,7 +36982,7 @@
         <v>2109</v>
       </c>
       <c r="I349" s="6" t="s">
-        <v>2252</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="350" spans="1:9" ht="13.5">
@@ -36844,7 +37011,7 @@
         <v>2109</v>
       </c>
       <c r="I350" s="6" t="s">
-        <v>2252</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="351" spans="1:9" ht="13.5">
@@ -36873,7 +37040,7 @@
         <v>2109</v>
       </c>
       <c r="I351" s="6" t="s">
-        <v>2252</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="352" spans="1:9" ht="13.5">
@@ -36902,7 +37069,7 @@
         <v>2109</v>
       </c>
       <c r="I352" s="6" t="s">
-        <v>2252</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="353" spans="1:9" ht="13.5">
@@ -36931,7 +37098,7 @@
         <v>2109</v>
       </c>
       <c r="I353" s="6" t="s">
-        <v>2252</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="354" spans="1:9" ht="13.5">
@@ -36960,7 +37127,7 @@
         <v>2109</v>
       </c>
       <c r="I354" s="6" t="s">
-        <v>2252</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="355" spans="1:9" ht="13.5">
@@ -36989,7 +37156,7 @@
         <v>2109</v>
       </c>
       <c r="I355" s="6" t="s">
-        <v>2252</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="356" spans="1:9" ht="13.5">
@@ -37018,7 +37185,7 @@
         <v>2109</v>
       </c>
       <c r="I356" s="6" t="s">
-        <v>2252</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="357" spans="1:9" ht="13.5">
@@ -37047,7 +37214,7 @@
         <v>2109</v>
       </c>
       <c r="I357" s="6" t="s">
-        <v>2252</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="358" spans="1:9" ht="13.5">
@@ -37076,7 +37243,7 @@
         <v>2109</v>
       </c>
       <c r="I358" s="6" t="s">
-        <v>2252</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="359" spans="1:9" ht="13.5">
@@ -37105,7 +37272,7 @@
         <v>2109</v>
       </c>
       <c r="I359" s="6" t="s">
-        <v>2252</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="360" spans="1:9" ht="13.5">
@@ -37134,7 +37301,7 @@
         <v>2109</v>
       </c>
       <c r="I360" s="6" t="s">
-        <v>2252</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="361" spans="1:9" ht="13.5">
@@ -37163,7 +37330,7 @@
         <v>2109</v>
       </c>
       <c r="I361" s="6" t="s">
-        <v>2252</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="362" spans="1:9" ht="13.5">
@@ -37192,7 +37359,7 @@
         <v>2109</v>
       </c>
       <c r="I362" s="6" t="s">
-        <v>2252</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="363" spans="1:9" ht="13.5">
@@ -37221,7 +37388,7 @@
         <v>2109</v>
       </c>
       <c r="I363" s="6" t="s">
-        <v>2252</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="364" spans="1:9" ht="13.5">
@@ -37250,7 +37417,7 @@
         <v>2109</v>
       </c>
       <c r="I364" s="6" t="s">
-        <v>2252</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="365" spans="1:9" ht="13.5">
@@ -37279,7 +37446,7 @@
         <v>2109</v>
       </c>
       <c r="I365" s="6" t="s">
-        <v>2252</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="366" spans="1:9" ht="13.5">
@@ -37308,7 +37475,7 @@
         <v>2109</v>
       </c>
       <c r="I366" s="6" t="s">
-        <v>2252</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="367" spans="1:9" ht="13.5">
@@ -37337,7 +37504,7 @@
         <v>2109</v>
       </c>
       <c r="I367" s="6" t="s">
-        <v>2252</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="368" spans="1:9" ht="13.5">
@@ -37366,7 +37533,7 @@
         <v>2109</v>
       </c>
       <c r="I368" s="6" t="s">
-        <v>2252</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="369" spans="1:10" ht="13.5">
@@ -37395,7 +37562,7 @@
         <v>2109</v>
       </c>
       <c r="I369" s="6" t="s">
-        <v>2252</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="370" spans="1:10" ht="13.5">
@@ -37424,7 +37591,7 @@
         <v>2109</v>
       </c>
       <c r="I370" s="6" t="s">
-        <v>2252</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="371" spans="1:10" ht="13.5">
@@ -52473,7 +52640,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>2245</v>
+        <v>2244</v>
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -52484,7 +52651,7 @@
         <v>1182</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>2242</v>
+        <v>2241</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -52506,7 +52673,7 @@
         <v>5</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>2246</v>
+        <v>2245</v>
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
@@ -52517,7 +52684,7 @@
         <v>7</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>2247</v>
+        <v>2246</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
@@ -52531,31 +52698,31 @@
         <v>10</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>2116</v>
+        <v>2115</v>
       </c>
       <c r="D7" s="12" t="s">
         <v>11</v>
       </c>
       <c r="E7" s="12" t="s">
+        <v>2116</v>
+      </c>
+      <c r="F7" s="12" t="s">
         <v>2117</v>
       </c>
-      <c r="F7" s="12" t="s">
+      <c r="G7" s="12" t="s">
         <v>2118</v>
       </c>
-      <c r="G7" s="12" t="s">
+      <c r="H7" s="12" t="s">
         <v>2119</v>
       </c>
-      <c r="H7" s="12" t="s">
+      <c r="I7" s="12" t="s">
         <v>2120</v>
       </c>
-      <c r="I7" s="12" t="s">
+      <c r="J7" s="13" t="s">
         <v>2121</v>
       </c>
-      <c r="J7" s="13" t="s">
+      <c r="K7" s="12" t="s">
         <v>2122</v>
-      </c>
-      <c r="K7" s="12" t="s">
-        <v>2123</v>
       </c>
       <c r="L7" s="12" t="s">
         <v>13</v>
@@ -52564,7 +52731,7 @@
         <v>1186</v>
       </c>
       <c r="N7" s="12" t="s">
-        <v>2124</v>
+        <v>2123</v>
       </c>
       <c r="O7" s="5" t="s">
         <v>14</v>
@@ -52584,13 +52751,13 @@
         <v>982</v>
       </c>
       <c r="D8" t="s">
+        <v>2124</v>
+      </c>
+      <c r="H8" t="s">
         <v>2125</v>
       </c>
-      <c r="H8" t="s">
-        <v>2126</v>
-      </c>
       <c r="J8" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="L8" t="s">
         <v>2108</v>
@@ -52598,6 +52765,10 @@
       <c r="M8">
         <v>1</v>
       </c>
+      <c r="N8" s="1" t="s">
+        <v>2257</v>
+      </c>
+      <c r="O8" s="1"/>
     </row>
     <row r="9" spans="1:16">
       <c r="A9" t="s">
@@ -52610,13 +52781,13 @@
         <v>984</v>
       </c>
       <c r="D9" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="H9" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="J9" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="L9" t="s">
         <v>2108</v>
@@ -52624,6 +52795,10 @@
       <c r="M9">
         <v>1</v>
       </c>
+      <c r="N9" s="1" t="s">
+        <v>2257</v>
+      </c>
+      <c r="O9" s="1"/>
     </row>
     <row r="10" spans="1:16" ht="13.5">
       <c r="A10" t="s">
@@ -52633,13 +52808,13 @@
         <v>431</v>
       </c>
       <c r="C10" t="s">
+        <v>2127</v>
+      </c>
+      <c r="D10" t="s">
         <v>2128</v>
       </c>
-      <c r="D10" t="s">
-        <v>2129</v>
-      </c>
       <c r="J10" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="L10" s="2" t="s">
         <v>1590</v>
@@ -52647,8 +52822,11 @@
       <c r="M10">
         <v>1</v>
       </c>
+      <c r="N10" s="1" t="s">
+        <v>2257</v>
+      </c>
       <c r="P10" s="2" t="s">
-        <v>2251</v>
+        <v>2249</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -52659,16 +52837,16 @@
         <v>431</v>
       </c>
       <c r="C11" t="s">
+        <v>2129</v>
+      </c>
+      <c r="D11" t="s">
         <v>2130</v>
       </c>
-      <c r="D11" t="s">
-        <v>2131</v>
-      </c>
       <c r="F11" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="H11" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="L11" t="s">
         <v>2108</v>
@@ -52676,6 +52854,10 @@
       <c r="M11">
         <v>1</v>
       </c>
+      <c r="N11" s="1" t="s">
+        <v>2257</v>
+      </c>
+      <c r="O11" s="1"/>
     </row>
     <row r="12" spans="1:16">
       <c r="A12" t="s">
@@ -52685,10 +52867,10 @@
         <v>431</v>
       </c>
       <c r="C12" t="s">
-        <v>2132</v>
+        <v>2131</v>
       </c>
       <c r="E12" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="L12" t="s">
         <v>2108</v>
@@ -52696,6 +52878,10 @@
       <c r="M12">
         <v>1</v>
       </c>
+      <c r="N12" s="1" t="s">
+        <v>2257</v>
+      </c>
+      <c r="O12" s="1"/>
     </row>
     <row r="13" spans="1:16">
       <c r="A13" t="s">
@@ -52705,10 +52891,10 @@
         <v>431</v>
       </c>
       <c r="C13" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
       <c r="E13" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="L13" t="s">
         <v>2108</v>
@@ -52716,6 +52902,10 @@
       <c r="M13">
         <v>1</v>
       </c>
+      <c r="N13" s="1" t="s">
+        <v>2257</v>
+      </c>
+      <c r="O13" s="1"/>
     </row>
     <row r="14" spans="1:16">
       <c r="A14" t="s">
@@ -52725,10 +52915,10 @@
         <v>431</v>
       </c>
       <c r="C14" t="s">
-        <v>2134</v>
+        <v>2133</v>
       </c>
       <c r="E14" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="L14" t="s">
         <v>2108</v>
@@ -52736,6 +52926,10 @@
       <c r="M14">
         <v>1</v>
       </c>
+      <c r="N14" s="1" t="s">
+        <v>2257</v>
+      </c>
+      <c r="O14" s="1"/>
     </row>
     <row r="15" spans="1:16" ht="13.5">
       <c r="A15" t="s">
@@ -52748,10 +52942,10 @@
         <v>986</v>
       </c>
       <c r="D15" t="s">
-        <v>2135</v>
+        <v>2134</v>
       </c>
       <c r="J15" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="L15" s="2" t="s">
         <v>1590</v>
@@ -52759,8 +52953,11 @@
       <c r="M15">
         <v>1</v>
       </c>
+      <c r="N15" s="1" t="s">
+        <v>2257</v>
+      </c>
       <c r="P15" s="2" t="s">
-        <v>2251</v>
+        <v>2249</v>
       </c>
     </row>
     <row r="16" spans="1:16" ht="13.5">
@@ -52774,10 +52971,10 @@
         <v>988</v>
       </c>
       <c r="D16" t="s">
-        <v>2136</v>
+        <v>2135</v>
       </c>
       <c r="J16" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="L16" s="2" t="s">
         <v>1590</v>
@@ -52785,8 +52982,11 @@
       <c r="M16">
         <v>1</v>
       </c>
+      <c r="N16" s="1" t="s">
+        <v>2257</v>
+      </c>
       <c r="P16" s="2" t="s">
-        <v>2251</v>
+        <v>2249</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -52797,10 +52997,10 @@
         <v>431</v>
       </c>
       <c r="C17" t="s">
-        <v>2137</v>
+        <v>2136</v>
       </c>
       <c r="E17" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="L17" t="s">
         <v>2108</v>
@@ -52808,6 +53008,10 @@
       <c r="M17">
         <v>1</v>
       </c>
+      <c r="N17" s="1" t="s">
+        <v>2257</v>
+      </c>
+      <c r="O17" s="1"/>
     </row>
     <row r="18" spans="1:16">
       <c r="A18" t="s">
@@ -52817,13 +53021,13 @@
         <v>431</v>
       </c>
       <c r="C18" t="s">
+        <v>2137</v>
+      </c>
+      <c r="D18" t="s">
         <v>2138</v>
       </c>
-      <c r="D18" t="s">
-        <v>2139</v>
-      </c>
       <c r="F18" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="L18" t="s">
         <v>2108</v>
@@ -52831,6 +53035,10 @@
       <c r="M18">
         <v>1</v>
       </c>
+      <c r="N18" s="1" t="s">
+        <v>2257</v>
+      </c>
+      <c r="O18" s="1"/>
     </row>
     <row r="19" spans="1:16">
       <c r="A19" t="s">
@@ -52840,16 +53048,16 @@
         <v>431</v>
       </c>
       <c r="C19" t="s">
+        <v>2139</v>
+      </c>
+      <c r="D19" t="s">
         <v>2140</v>
       </c>
-      <c r="D19" t="s">
-        <v>2141</v>
-      </c>
       <c r="F19" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="J19" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="L19" t="s">
         <v>2108</v>
@@ -52857,6 +53065,10 @@
       <c r="M19">
         <v>1</v>
       </c>
+      <c r="N19" s="1" t="s">
+        <v>2257</v>
+      </c>
+      <c r="O19" s="1"/>
     </row>
     <row r="20" spans="1:16">
       <c r="A20" t="s">
@@ -52866,16 +53078,16 @@
         <v>431</v>
       </c>
       <c r="C20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="D20" t="s">
         <v>2142</v>
       </c>
-      <c r="D20" t="s">
-        <v>2143</v>
-      </c>
       <c r="F20" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="J20" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="L20" t="s">
         <v>2108</v>
@@ -52883,6 +53095,10 @@
       <c r="M20">
         <v>1</v>
       </c>
+      <c r="N20" s="1" t="s">
+        <v>2257</v>
+      </c>
+      <c r="O20" s="1"/>
     </row>
     <row r="21" spans="1:16">
       <c r="A21" t="s">
@@ -52892,16 +53108,16 @@
         <v>431</v>
       </c>
       <c r="C21" t="s">
+        <v>2143</v>
+      </c>
+      <c r="D21" t="s">
         <v>2144</v>
       </c>
-      <c r="D21" t="s">
-        <v>2145</v>
-      </c>
       <c r="F21" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="H21" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="L21" t="s">
         <v>2108</v>
@@ -52909,6 +53125,10 @@
       <c r="M21">
         <v>1</v>
       </c>
+      <c r="N21" s="1" t="s">
+        <v>2257</v>
+      </c>
+      <c r="O21" s="1"/>
     </row>
     <row r="22" spans="1:16">
       <c r="A22" t="s">
@@ -52921,10 +53141,10 @@
         <v>458</v>
       </c>
       <c r="D22" t="s">
-        <v>2146</v>
+        <v>2145</v>
       </c>
       <c r="H22" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="L22" t="s">
         <v>2108</v>
@@ -52932,6 +53152,10 @@
       <c r="M22">
         <v>1</v>
       </c>
+      <c r="N22" s="1" t="s">
+        <v>2257</v>
+      </c>
+      <c r="O22" s="1"/>
     </row>
     <row r="23" spans="1:16">
       <c r="A23" t="s">
@@ -52941,16 +53165,16 @@
         <v>431</v>
       </c>
       <c r="C23" t="s">
+        <v>2146</v>
+      </c>
+      <c r="D23" t="s">
         <v>2147</v>
       </c>
-      <c r="D23" t="s">
-        <v>2148</v>
-      </c>
       <c r="H23" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="J23" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="L23" t="s">
         <v>2108</v>
@@ -52958,8 +53182,12 @@
       <c r="M23">
         <v>1</v>
       </c>
-    </row>
-    <row r="24" spans="1:16">
+      <c r="N23" s="1" t="s">
+        <v>2257</v>
+      </c>
+      <c r="O23" s="1"/>
+    </row>
+    <row r="24" spans="1:16" ht="13.5">
       <c r="A24" t="s">
         <v>75</v>
       </c>
@@ -52970,22 +53198,28 @@
         <v>982</v>
       </c>
       <c r="D24" t="s">
-        <v>2149</v>
+        <v>2148</v>
       </c>
       <c r="H24" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="J24" t="s">
-        <v>2126</v>
-      </c>
-      <c r="L24" t="s">
-        <v>2108</v>
+        <v>2125</v>
+      </c>
+      <c r="L24" s="2" t="s">
+        <v>2258</v>
       </c>
       <c r="M24">
         <v>1</v>
       </c>
-    </row>
-    <row r="25" spans="1:16">
+      <c r="N24" s="1" t="s">
+        <v>2257</v>
+      </c>
+      <c r="O24" s="1" t="s">
+        <v>2259</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" ht="13.5">
       <c r="A25" t="s">
         <v>75</v>
       </c>
@@ -52996,22 +53230,28 @@
         <v>984</v>
       </c>
       <c r="D25" t="s">
-        <v>2150</v>
+        <v>2149</v>
       </c>
       <c r="H25" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="J25" t="s">
-        <v>2126</v>
-      </c>
-      <c r="L25" t="s">
-        <v>2108</v>
+        <v>2125</v>
+      </c>
+      <c r="L25" s="2" t="s">
+        <v>2258</v>
       </c>
       <c r="M25">
         <v>1</v>
       </c>
-    </row>
-    <row r="26" spans="1:16">
+      <c r="N25" s="1" t="s">
+        <v>2257</v>
+      </c>
+      <c r="O25" s="1" t="s">
+        <v>2259</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" ht="13.5">
       <c r="A26" t="s">
         <v>75</v>
       </c>
@@ -53019,25 +53259,31 @@
         <v>456</v>
       </c>
       <c r="C26" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
       <c r="D26" t="s">
-        <v>2151</v>
+        <v>2150</v>
       </c>
       <c r="H26" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="J26" t="s">
-        <v>2126</v>
-      </c>
-      <c r="L26" t="s">
-        <v>2108</v>
+        <v>2125</v>
+      </c>
+      <c r="L26" s="2" t="s">
+        <v>2258</v>
       </c>
       <c r="M26">
         <v>1</v>
       </c>
-    </row>
-    <row r="27" spans="1:16">
+      <c r="N26" s="1" t="s">
+        <v>2257</v>
+      </c>
+      <c r="O26" s="1" t="s">
+        <v>2259</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" ht="13.5">
       <c r="A27" t="s">
         <v>75</v>
       </c>
@@ -53045,25 +53291,31 @@
         <v>456</v>
       </c>
       <c r="C27" t="s">
-        <v>2130</v>
+        <v>2129</v>
       </c>
       <c r="D27" t="s">
-        <v>2152</v>
+        <v>2151</v>
       </c>
       <c r="F27" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="H27" t="s">
-        <v>2126</v>
-      </c>
-      <c r="L27" t="s">
-        <v>2108</v>
+        <v>2125</v>
+      </c>
+      <c r="L27" s="2" t="s">
+        <v>2258</v>
       </c>
       <c r="M27">
         <v>1</v>
       </c>
-    </row>
-    <row r="28" spans="1:16">
+      <c r="N27" s="1" t="s">
+        <v>2257</v>
+      </c>
+      <c r="O27" s="1" t="s">
+        <v>2259</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" ht="13.5">
       <c r="A28" t="s">
         <v>75</v>
       </c>
@@ -53071,16 +53323,22 @@
         <v>456</v>
       </c>
       <c r="C28" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
       <c r="E28" t="s">
-        <v>2126</v>
-      </c>
-      <c r="L28" t="s">
-        <v>2108</v>
+        <v>2125</v>
+      </c>
+      <c r="L28" s="2" t="s">
+        <v>2258</v>
       </c>
       <c r="M28">
         <v>1</v>
+      </c>
+      <c r="N28" s="1" t="s">
+        <v>2257</v>
+      </c>
+      <c r="O28" s="1" t="s">
+        <v>2259</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -53091,10 +53349,10 @@
         <v>456</v>
       </c>
       <c r="C29" t="s">
-        <v>2153</v>
+        <v>2152</v>
       </c>
       <c r="E29" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="L29" t="s">
         <v>2108</v>
@@ -53102,6 +53360,10 @@
       <c r="M29">
         <v>1</v>
       </c>
+      <c r="N29" s="1" t="s">
+        <v>2257</v>
+      </c>
+      <c r="O29" s="1"/>
     </row>
     <row r="30" spans="1:16" ht="13.5">
       <c r="A30" t="s">
@@ -53114,10 +53376,10 @@
         <v>986</v>
       </c>
       <c r="D30" t="s">
-        <v>2154</v>
+        <v>2153</v>
       </c>
       <c r="J30" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="L30" s="2" t="s">
         <v>1590</v>
@@ -53125,8 +53387,11 @@
       <c r="M30">
         <v>1</v>
       </c>
+      <c r="N30" s="1" t="s">
+        <v>2257</v>
+      </c>
       <c r="P30" s="2" t="s">
-        <v>2251</v>
+        <v>2249</v>
       </c>
     </row>
     <row r="31" spans="1:16" ht="13.5">
@@ -53140,10 +53405,10 @@
         <v>988</v>
       </c>
       <c r="D31" t="s">
-        <v>2155</v>
+        <v>2154</v>
       </c>
       <c r="J31" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="L31" s="2" t="s">
         <v>1590</v>
@@ -53151,8 +53416,11 @@
       <c r="M31">
         <v>1</v>
       </c>
+      <c r="N31" s="1" t="s">
+        <v>2257</v>
+      </c>
       <c r="P31" s="2" t="s">
-        <v>2251</v>
+        <v>2249</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -53163,10 +53431,10 @@
         <v>456</v>
       </c>
       <c r="C32" t="s">
-        <v>2137</v>
+        <v>2136</v>
       </c>
       <c r="E32" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="L32" t="s">
         <v>2108</v>
@@ -53174,8 +53442,11 @@
       <c r="M32">
         <v>1</v>
       </c>
-    </row>
-    <row r="33" spans="1:13">
+      <c r="N32" s="1" t="s">
+        <v>2257</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" ht="13.5">
       <c r="A33" t="s">
         <v>75</v>
       </c>
@@ -53183,25 +53454,31 @@
         <v>456</v>
       </c>
       <c r="C33" t="s">
-        <v>2138</v>
+        <v>2137</v>
       </c>
       <c r="D33" t="s">
-        <v>2156</v>
+        <v>2155</v>
       </c>
       <c r="F33" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="H33" t="s">
-        <v>2126</v>
-      </c>
-      <c r="L33" t="s">
-        <v>2108</v>
+        <v>2125</v>
+      </c>
+      <c r="L33" s="2" t="s">
+        <v>2258</v>
       </c>
       <c r="M33">
         <v>1</v>
       </c>
-    </row>
-    <row r="34" spans="1:13">
+      <c r="N33" s="1" t="s">
+        <v>2257</v>
+      </c>
+      <c r="O33" s="1" t="s">
+        <v>2259</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" ht="13.5">
       <c r="A34" t="s">
         <v>75</v>
       </c>
@@ -53209,28 +53486,34 @@
         <v>456</v>
       </c>
       <c r="C34" t="s">
-        <v>2140</v>
+        <v>2139</v>
       </c>
       <c r="D34" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="F34" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="H34" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="J34" t="s">
-        <v>2126</v>
-      </c>
-      <c r="L34" t="s">
-        <v>2108</v>
+        <v>2125</v>
+      </c>
+      <c r="L34" s="2" t="s">
+        <v>2258</v>
       </c>
       <c r="M34">
         <v>1</v>
       </c>
-    </row>
-    <row r="35" spans="1:13">
+      <c r="N34" s="1" t="s">
+        <v>2257</v>
+      </c>
+      <c r="O34" s="1" t="s">
+        <v>2259</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15">
       <c r="A35" t="s">
         <v>75</v>
       </c>
@@ -53238,16 +53521,16 @@
         <v>456</v>
       </c>
       <c r="C35" t="s">
-        <v>2142</v>
+        <v>2141</v>
       </c>
       <c r="D35" t="s">
-        <v>2158</v>
+        <v>2157</v>
       </c>
       <c r="F35" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="J35" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="L35" t="s">
         <v>2108</v>
@@ -53255,8 +53538,11 @@
       <c r="M35">
         <v>1</v>
       </c>
-    </row>
-    <row r="36" spans="1:13">
+      <c r="N35" s="1" t="s">
+        <v>2257</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" ht="13.5">
       <c r="A36" t="s">
         <v>75</v>
       </c>
@@ -53264,25 +53550,31 @@
         <v>456</v>
       </c>
       <c r="C36" t="s">
-        <v>2144</v>
+        <v>2143</v>
       </c>
       <c r="D36" t="s">
-        <v>2159</v>
+        <v>2158</v>
       </c>
       <c r="F36" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="H36" t="s">
-        <v>2126</v>
-      </c>
-      <c r="L36" t="s">
-        <v>2108</v>
+        <v>2125</v>
+      </c>
+      <c r="L36" s="2" t="s">
+        <v>2258</v>
       </c>
       <c r="M36">
         <v>1</v>
       </c>
-    </row>
-    <row r="37" spans="1:13">
+      <c r="N36" s="1" t="s">
+        <v>2257</v>
+      </c>
+      <c r="O36" s="1" t="s">
+        <v>2259</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" ht="13.5">
       <c r="A37" t="s">
         <v>75</v>
       </c>
@@ -53296,16 +53588,22 @@
         <v>459</v>
       </c>
       <c r="H37" t="s">
-        <v>2126</v>
-      </c>
-      <c r="L37" t="s">
-        <v>2108</v>
+        <v>2125</v>
+      </c>
+      <c r="L37" s="2" t="s">
+        <v>2258</v>
       </c>
       <c r="M37">
         <v>1</v>
       </c>
-    </row>
-    <row r="38" spans="1:13">
+      <c r="N37" s="1" t="s">
+        <v>2257</v>
+      </c>
+      <c r="O37" s="1" t="s">
+        <v>2259</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" ht="13.5">
       <c r="A38" t="s">
         <v>75</v>
       </c>
@@ -53313,25 +53611,31 @@
         <v>456</v>
       </c>
       <c r="C38" t="s">
-        <v>2147</v>
+        <v>2146</v>
       </c>
       <c r="D38" t="s">
         <v>459</v>
       </c>
       <c r="H38" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="J38" t="s">
-        <v>2126</v>
-      </c>
-      <c r="L38" t="s">
-        <v>2108</v>
+        <v>2125</v>
+      </c>
+      <c r="L38" s="2" t="s">
+        <v>2258</v>
       </c>
       <c r="M38">
         <v>1</v>
       </c>
-    </row>
-    <row r="39" spans="1:13">
+      <c r="N38" s="1" t="s">
+        <v>2257</v>
+      </c>
+      <c r="O38" s="1" t="s">
+        <v>2259</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15">
       <c r="A39" t="s">
         <v>75</v>
       </c>
@@ -53339,10 +53643,10 @@
         <v>762</v>
       </c>
       <c r="C39" t="s">
-        <v>2160</v>
+        <v>2159</v>
       </c>
       <c r="E39" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="L39" t="s">
         <v>2108</v>
@@ -53350,8 +53654,11 @@
       <c r="M39">
         <v>1</v>
       </c>
-    </row>
-    <row r="40" spans="1:13">
+      <c r="N39" s="1" t="s">
+        <v>2257</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15">
       <c r="A40" t="s">
         <v>75</v>
       </c>
@@ -53359,10 +53666,10 @@
         <v>762</v>
       </c>
       <c r="C40" t="s">
-        <v>2161</v>
+        <v>2160</v>
       </c>
       <c r="E40" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="L40" t="s">
         <v>2108</v>
@@ -53370,8 +53677,11 @@
       <c r="M40">
         <v>1</v>
       </c>
-    </row>
-    <row r="41" spans="1:13">
+      <c r="N40" s="1" t="s">
+        <v>2257</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" ht="13.5">
       <c r="A41" t="s">
         <v>75</v>
       </c>
@@ -53379,25 +53689,31 @@
         <v>762</v>
       </c>
       <c r="C41" t="s">
+        <v>2161</v>
+      </c>
+      <c r="D41" t="s">
         <v>2162</v>
       </c>
-      <c r="D41" t="s">
-        <v>2163</v>
-      </c>
       <c r="F41" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="H41" t="s">
-        <v>2126</v>
-      </c>
-      <c r="L41" t="s">
-        <v>2108</v>
+        <v>2125</v>
+      </c>
+      <c r="L41" s="2" t="s">
+        <v>2258</v>
       </c>
       <c r="M41">
         <v>1</v>
       </c>
-    </row>
-    <row r="42" spans="1:13">
+      <c r="N41" s="1" t="s">
+        <v>2257</v>
+      </c>
+      <c r="O41" s="1" t="s">
+        <v>2260</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15">
       <c r="A42" t="s">
         <v>75</v>
       </c>
@@ -53408,13 +53724,13 @@
         <v>988</v>
       </c>
       <c r="D42" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="F42" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="J42" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="L42" t="s">
         <v>2108</v>
@@ -53422,8 +53738,11 @@
       <c r="M42">
         <v>1</v>
       </c>
-    </row>
-    <row r="43" spans="1:13">
+      <c r="N42" s="1" t="s">
+        <v>2257</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15">
       <c r="A43" t="s">
         <v>75</v>
       </c>
@@ -53431,10 +53750,10 @@
         <v>762</v>
       </c>
       <c r="C43" t="s">
-        <v>2137</v>
+        <v>2136</v>
       </c>
       <c r="E43" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="L43" t="s">
         <v>2108</v>
@@ -53442,8 +53761,11 @@
       <c r="M43">
         <v>1</v>
       </c>
-    </row>
-    <row r="44" spans="1:13">
+      <c r="N43" s="1" t="s">
+        <v>2257</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" ht="13.5">
       <c r="A44" t="s">
         <v>75</v>
       </c>
@@ -53451,28 +53773,34 @@
         <v>762</v>
       </c>
       <c r="C44" t="s">
-        <v>2140</v>
+        <v>2139</v>
       </c>
       <c r="D44" t="s">
-        <v>2165</v>
+        <v>2164</v>
       </c>
       <c r="F44" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="H44" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="J44" t="s">
-        <v>2126</v>
-      </c>
-      <c r="L44" t="s">
-        <v>2108</v>
+        <v>2125</v>
+      </c>
+      <c r="L44" s="2" t="s">
+        <v>2258</v>
       </c>
       <c r="M44">
         <v>1</v>
       </c>
-    </row>
-    <row r="45" spans="1:13">
+      <c r="N44" s="1" t="s">
+        <v>2257</v>
+      </c>
+      <c r="O44" s="1" t="s">
+        <v>2260</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15">
       <c r="A45" t="s">
         <v>75</v>
       </c>
@@ -53480,13 +53808,13 @@
         <v>762</v>
       </c>
       <c r="C45" t="s">
-        <v>2142</v>
+        <v>2141</v>
       </c>
       <c r="D45" t="s">
-        <v>2166</v>
+        <v>2165</v>
       </c>
       <c r="F45" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="L45" t="s">
         <v>2108</v>
@@ -53494,8 +53822,11 @@
       <c r="M45">
         <v>1</v>
       </c>
-    </row>
-    <row r="46" spans="1:13">
+      <c r="N45" s="1" t="s">
+        <v>2257</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" ht="13.5">
       <c r="A46" t="s">
         <v>75</v>
       </c>
@@ -53503,28 +53834,34 @@
         <v>762</v>
       </c>
       <c r="C46" t="s">
+        <v>2166</v>
+      </c>
+      <c r="D46" t="s">
         <v>2167</v>
       </c>
-      <c r="D46" t="s">
-        <v>2168</v>
-      </c>
       <c r="F46" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="H46" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="I46" t="s">
-        <v>2126</v>
-      </c>
-      <c r="L46" t="s">
-        <v>2108</v>
+        <v>2125</v>
+      </c>
+      <c r="L46" s="2" t="s">
+        <v>2258</v>
       </c>
       <c r="M46">
         <v>1</v>
       </c>
-    </row>
-    <row r="47" spans="1:13">
+      <c r="N46" s="1" t="s">
+        <v>2257</v>
+      </c>
+      <c r="O46" s="1" t="s">
+        <v>2260</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15" ht="13.5">
       <c r="A47" t="s">
         <v>75</v>
       </c>
@@ -53538,16 +53875,22 @@
         <v>983</v>
       </c>
       <c r="H47" t="s">
-        <v>2126</v>
-      </c>
-      <c r="L47" t="s">
-        <v>2108</v>
+        <v>2125</v>
+      </c>
+      <c r="L47" s="2" t="s">
+        <v>2258</v>
       </c>
       <c r="M47">
         <v>1</v>
       </c>
-    </row>
-    <row r="48" spans="1:13">
+      <c r="N47" s="1" t="s">
+        <v>2257</v>
+      </c>
+      <c r="O47" s="1" t="s">
+        <v>2260</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15" ht="13.5">
       <c r="A48" t="s">
         <v>75</v>
       </c>
@@ -53561,16 +53904,22 @@
         <v>985</v>
       </c>
       <c r="H48" t="s">
-        <v>2126</v>
-      </c>
-      <c r="L48" t="s">
-        <v>2108</v>
+        <v>2125</v>
+      </c>
+      <c r="L48" s="2" t="s">
+        <v>2258</v>
       </c>
       <c r="M48">
         <v>1</v>
       </c>
-    </row>
-    <row r="49" spans="1:16">
+      <c r="N48" s="1" t="s">
+        <v>2257</v>
+      </c>
+      <c r="O48" s="1" t="s">
+        <v>2260</v>
+      </c>
+    </row>
+    <row r="49" spans="1:16" ht="13.5">
       <c r="A49" t="s">
         <v>75</v>
       </c>
@@ -53578,22 +53927,28 @@
         <v>981</v>
       </c>
       <c r="C49" t="s">
-        <v>2130</v>
+        <v>2129</v>
       </c>
       <c r="D49" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
       <c r="F49" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="H49" t="s">
-        <v>2126</v>
-      </c>
-      <c r="L49" t="s">
-        <v>2108</v>
+        <v>2125</v>
+      </c>
+      <c r="L49" s="2" t="s">
+        <v>2258</v>
       </c>
       <c r="M49">
         <v>1</v>
+      </c>
+      <c r="N49" s="1" t="s">
+        <v>2257</v>
+      </c>
+      <c r="O49" s="1" t="s">
+        <v>2260</v>
       </c>
     </row>
     <row r="50" spans="1:16" ht="13.5">
@@ -53610,7 +53965,7 @@
         <v>987</v>
       </c>
       <c r="J50" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="L50" s="2" t="s">
         <v>1590</v>
@@ -53618,8 +53973,11 @@
       <c r="M50">
         <v>1</v>
       </c>
+      <c r="N50" s="1" t="s">
+        <v>2257</v>
+      </c>
       <c r="P50" t="s">
-        <v>2250</v>
+        <v>2248</v>
       </c>
     </row>
     <row r="51" spans="1:16" ht="13.5">
@@ -53636,7 +53994,7 @@
         <v>989</v>
       </c>
       <c r="J51" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="L51" s="2" t="s">
         <v>1590</v>
@@ -53644,11 +54002,14 @@
       <c r="M51">
         <v>1</v>
       </c>
+      <c r="N51" s="1" t="s">
+        <v>2257</v>
+      </c>
       <c r="P51" s="2" t="s">
-        <v>2251</v>
-      </c>
-    </row>
-    <row r="52" spans="1:16">
+        <v>2249</v>
+      </c>
+    </row>
+    <row r="52" spans="1:16" ht="13.5">
       <c r="A52" t="s">
         <v>75</v>
       </c>
@@ -53656,25 +54017,31 @@
         <v>981</v>
       </c>
       <c r="C52" t="s">
-        <v>2140</v>
+        <v>2139</v>
       </c>
       <c r="D52" t="s">
-        <v>2170</v>
+        <v>2169</v>
       </c>
       <c r="F52" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="H52" t="s">
-        <v>2126</v>
-      </c>
-      <c r="L52" t="s">
-        <v>2108</v>
+        <v>2125</v>
+      </c>
+      <c r="L52" s="2" t="s">
+        <v>2258</v>
       </c>
       <c r="M52">
         <v>1</v>
       </c>
-    </row>
-    <row r="53" spans="1:16">
+      <c r="N52" s="1" t="s">
+        <v>2257</v>
+      </c>
+      <c r="O52" s="1" t="s">
+        <v>2260</v>
+      </c>
+    </row>
+    <row r="53" spans="1:16" ht="13.5">
       <c r="A53" t="s">
         <v>75</v>
       </c>
@@ -53682,28 +54049,34 @@
         <v>981</v>
       </c>
       <c r="C53" t="s">
-        <v>2144</v>
+        <v>2143</v>
       </c>
       <c r="D53" t="s">
-        <v>2171</v>
+        <v>2170</v>
       </c>
       <c r="F53" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="H53" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="J53" t="s">
-        <v>2126</v>
-      </c>
-      <c r="L53" t="s">
-        <v>2108</v>
+        <v>2125</v>
+      </c>
+      <c r="L53" s="2" t="s">
+        <v>2258</v>
       </c>
       <c r="M53">
         <v>1</v>
       </c>
-    </row>
-    <row r="54" spans="1:16">
+      <c r="N53" s="1" t="s">
+        <v>2257</v>
+      </c>
+      <c r="O53" s="1" t="s">
+        <v>2260</v>
+      </c>
+    </row>
+    <row r="54" spans="1:16" ht="13.5">
       <c r="A54" t="s">
         <v>75</v>
       </c>
@@ -53711,25 +54084,31 @@
         <v>981</v>
       </c>
       <c r="C54" t="s">
+        <v>2171</v>
+      </c>
+      <c r="D54" t="s">
         <v>2172</v>
       </c>
-      <c r="D54" t="s">
-        <v>2173</v>
-      </c>
       <c r="F54" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="H54" t="s">
-        <v>2126</v>
-      </c>
-      <c r="L54" t="s">
-        <v>2108</v>
+        <v>2125</v>
+      </c>
+      <c r="L54" s="2" t="s">
+        <v>2258</v>
       </c>
       <c r="M54">
         <v>1</v>
       </c>
-    </row>
-    <row r="55" spans="1:16">
+      <c r="N54" s="1" t="s">
+        <v>2257</v>
+      </c>
+      <c r="O54" s="1" t="s">
+        <v>2260</v>
+      </c>
+    </row>
+    <row r="55" spans="1:16" ht="13.5">
       <c r="A55" t="s">
         <v>75</v>
       </c>
@@ -53737,19 +54116,25 @@
         <v>1038</v>
       </c>
       <c r="C55" t="s">
+        <v>2173</v>
+      </c>
+      <c r="D55" t="s">
         <v>2174</v>
       </c>
-      <c r="D55" t="s">
-        <v>2175</v>
-      </c>
       <c r="H55" t="s">
-        <v>2126</v>
-      </c>
-      <c r="L55" t="s">
-        <v>2108</v>
+        <v>2125</v>
+      </c>
+      <c r="L55" s="2" t="s">
+        <v>2258</v>
       </c>
       <c r="M55">
         <v>1</v>
+      </c>
+      <c r="N55" s="1" t="s">
+        <v>2257</v>
+      </c>
+      <c r="O55" s="1" t="s">
+        <v>2260</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -53763,13 +54148,16 @@
         <v>1039</v>
       </c>
       <c r="E56" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="L56" t="s">
         <v>2108</v>
       </c>
       <c r="M56">
         <v>1</v>
+      </c>
+      <c r="N56" s="1" t="s">
+        <v>2257</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -53780,16 +54168,19 @@
         <v>1038</v>
       </c>
       <c r="C57" t="s">
-        <v>2176</v>
+        <v>2175</v>
       </c>
       <c r="G57" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="L57" t="s">
         <v>2108</v>
       </c>
       <c r="M57">
         <v>1</v>
+      </c>
+      <c r="N57" s="1" t="s">
+        <v>2257</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -53803,13 +54194,16 @@
         <v>988</v>
       </c>
       <c r="G58" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="L58" t="s">
         <v>2108</v>
       </c>
       <c r="M58">
         <v>1</v>
+      </c>
+      <c r="N58" s="1" t="s">
+        <v>2257</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -53820,16 +54214,19 @@
         <v>1038</v>
       </c>
       <c r="C59" t="s">
-        <v>2137</v>
+        <v>2136</v>
       </c>
       <c r="E59" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="L59" t="s">
         <v>2108</v>
       </c>
       <c r="M59">
         <v>1</v>
+      </c>
+      <c r="N59" s="1" t="s">
+        <v>2257</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -53840,10 +54237,10 @@
         <v>1038</v>
       </c>
       <c r="C60" t="s">
-        <v>2142</v>
+        <v>2141</v>
       </c>
       <c r="E60" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="L60" t="s">
         <v>2108</v>
@@ -53851,8 +54248,11 @@
       <c r="M60">
         <v>1</v>
       </c>
-    </row>
-    <row r="61" spans="1:16">
+      <c r="N60" s="1" t="s">
+        <v>2257</v>
+      </c>
+    </row>
+    <row r="61" spans="1:16" ht="13.5">
       <c r="A61" t="s">
         <v>75</v>
       </c>
@@ -53863,25 +54263,31 @@
         <v>1172</v>
       </c>
       <c r="D61" t="s">
-        <v>2177</v>
+        <v>2176</v>
       </c>
       <c r="F61" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="H61" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="I61" t="s">
-        <v>2126</v>
-      </c>
-      <c r="L61" t="s">
-        <v>2108</v>
+        <v>2125</v>
+      </c>
+      <c r="L61" s="2" t="s">
+        <v>2258</v>
       </c>
       <c r="M61">
         <v>1</v>
       </c>
-    </row>
-    <row r="62" spans="1:16">
+      <c r="N61" s="1" t="s">
+        <v>2257</v>
+      </c>
+      <c r="O61" s="1" t="s">
+        <v>2260</v>
+      </c>
+    </row>
+    <row r="62" spans="1:16" ht="13.5">
       <c r="A62" t="s">
         <v>75</v>
       </c>
@@ -53889,22 +54295,28 @@
         <v>1038</v>
       </c>
       <c r="C62" t="s">
+        <v>2177</v>
+      </c>
+      <c r="D62" t="s">
         <v>2178</v>
       </c>
-      <c r="D62" t="s">
-        <v>2179</v>
-      </c>
       <c r="H62" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="I62" t="s">
-        <v>2126</v>
-      </c>
-      <c r="L62" t="s">
-        <v>2108</v>
+        <v>2125</v>
+      </c>
+      <c r="L62" s="2" t="s">
+        <v>2258</v>
       </c>
       <c r="M62">
         <v>1</v>
+      </c>
+      <c r="N62" s="1" t="s">
+        <v>2257</v>
+      </c>
+      <c r="O62" s="1" t="s">
+        <v>2260</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -53918,7 +54330,7 @@
         <v>1041</v>
       </c>
       <c r="E63" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="L63" t="s">
         <v>2108</v>
@@ -53926,8 +54338,11 @@
       <c r="M63">
         <v>1</v>
       </c>
-    </row>
-    <row r="64" spans="1:16">
+      <c r="N63" s="1" t="s">
+        <v>2257</v>
+      </c>
+    </row>
+    <row r="64" spans="1:16" ht="13.5">
       <c r="A64" t="s">
         <v>75</v>
       </c>
@@ -53935,28 +54350,34 @@
         <v>1069</v>
       </c>
       <c r="C64" t="s">
+        <v>2179</v>
+      </c>
+      <c r="D64" t="s">
         <v>2180</v>
       </c>
-      <c r="D64" t="s">
-        <v>2181</v>
-      </c>
       <c r="F64" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="H64" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="I64" t="s">
-        <v>2126</v>
-      </c>
-      <c r="L64" t="s">
-        <v>2108</v>
+        <v>2125</v>
+      </c>
+      <c r="L64" s="2" t="s">
+        <v>2258</v>
       </c>
       <c r="M64">
         <v>1</v>
       </c>
-    </row>
-    <row r="65" spans="1:13">
+      <c r="N64" s="1" t="s">
+        <v>2257</v>
+      </c>
+      <c r="O64" s="1" t="s">
+        <v>2260</v>
+      </c>
+    </row>
+    <row r="65" spans="1:15">
       <c r="A65" t="s">
         <v>75</v>
       </c>
@@ -53964,10 +54385,10 @@
         <v>1069</v>
       </c>
       <c r="C65" t="s">
-        <v>2182</v>
+        <v>2181</v>
       </c>
       <c r="E65" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="L65" t="s">
         <v>2108</v>
@@ -53975,8 +54396,11 @@
       <c r="M65">
         <v>1</v>
       </c>
-    </row>
-    <row r="66" spans="1:13">
+      <c r="N65" s="1" t="s">
+        <v>2257</v>
+      </c>
+    </row>
+    <row r="66" spans="1:15">
       <c r="A66" t="s">
         <v>75</v>
       </c>
@@ -53984,10 +54408,10 @@
         <v>1069</v>
       </c>
       <c r="C66" t="s">
-        <v>2183</v>
+        <v>2182</v>
       </c>
       <c r="E66" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="L66" t="s">
         <v>2108</v>
@@ -53995,8 +54419,11 @@
       <c r="M66">
         <v>1</v>
       </c>
-    </row>
-    <row r="67" spans="1:13">
+      <c r="N66" s="1" t="s">
+        <v>2257</v>
+      </c>
+    </row>
+    <row r="67" spans="1:15" ht="13.5">
       <c r="A67" t="s">
         <v>75</v>
       </c>
@@ -54004,28 +54431,34 @@
         <v>1069</v>
       </c>
       <c r="C67" t="s">
+        <v>2183</v>
+      </c>
+      <c r="D67" t="s">
         <v>2184</v>
       </c>
-      <c r="D67" t="s">
-        <v>2185</v>
-      </c>
       <c r="F67" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="H67" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="I67" t="s">
-        <v>2126</v>
-      </c>
-      <c r="L67" t="s">
-        <v>2108</v>
+        <v>2125</v>
+      </c>
+      <c r="L67" s="2" t="s">
+        <v>2258</v>
       </c>
       <c r="M67">
         <v>1</v>
       </c>
-    </row>
-    <row r="68" spans="1:13">
+      <c r="N67" s="1" t="s">
+        <v>2257</v>
+      </c>
+      <c r="O67" s="1" t="s">
+        <v>2260</v>
+      </c>
+    </row>
+    <row r="68" spans="1:15" ht="13.5">
       <c r="A68" t="s">
         <v>75</v>
       </c>
@@ -54033,28 +54466,34 @@
         <v>1069</v>
       </c>
       <c r="C68" t="s">
+        <v>2185</v>
+      </c>
+      <c r="D68" t="s">
         <v>2186</v>
       </c>
-      <c r="D68" t="s">
-        <v>2187</v>
-      </c>
       <c r="F68" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="H68" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="J68" t="s">
-        <v>2126</v>
-      </c>
-      <c r="L68" t="s">
-        <v>2108</v>
+        <v>2125</v>
+      </c>
+      <c r="L68" s="2" t="s">
+        <v>2258</v>
       </c>
       <c r="M68">
         <v>1</v>
       </c>
-    </row>
-    <row r="69" spans="1:13">
+      <c r="N68" s="1" t="s">
+        <v>2257</v>
+      </c>
+      <c r="O68" s="1" t="s">
+        <v>2260</v>
+      </c>
+    </row>
+    <row r="69" spans="1:15" ht="13.5">
       <c r="A69" t="s">
         <v>75</v>
       </c>
@@ -54062,25 +54501,31 @@
         <v>1069</v>
       </c>
       <c r="C69" t="s">
+        <v>2187</v>
+      </c>
+      <c r="D69" t="s">
         <v>2188</v>
       </c>
-      <c r="D69" t="s">
-        <v>2189</v>
-      </c>
       <c r="H69" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="I69" t="s">
-        <v>2126</v>
-      </c>
-      <c r="L69" t="s">
-        <v>2108</v>
+        <v>2125</v>
+      </c>
+      <c r="L69" s="2" t="s">
+        <v>2258</v>
       </c>
       <c r="M69">
         <v>1</v>
       </c>
-    </row>
-    <row r="70" spans="1:13">
+      <c r="N69" s="1" t="s">
+        <v>2257</v>
+      </c>
+      <c r="O69" s="1" t="s">
+        <v>2260</v>
+      </c>
+    </row>
+    <row r="70" spans="1:15" ht="13.5">
       <c r="A70" t="s">
         <v>75</v>
       </c>
@@ -54094,16 +54539,22 @@
         <v>1071</v>
       </c>
       <c r="H70" t="s">
-        <v>2126</v>
-      </c>
-      <c r="L70" t="s">
-        <v>2108</v>
+        <v>2125</v>
+      </c>
+      <c r="L70" s="2" t="s">
+        <v>2258</v>
       </c>
       <c r="M70">
         <v>1</v>
       </c>
-    </row>
-    <row r="71" spans="1:13">
+      <c r="N70" s="1" t="s">
+        <v>2257</v>
+      </c>
+      <c r="O70" s="1" t="s">
+        <v>2260</v>
+      </c>
+    </row>
+    <row r="71" spans="1:15">
       <c r="A71" t="s">
         <v>75</v>
       </c>
@@ -54114,7 +54565,7 @@
         <v>1072</v>
       </c>
       <c r="E71" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="L71" t="s">
         <v>2108</v>
@@ -54122,8 +54573,11 @@
       <c r="M71">
         <v>1</v>
       </c>
-    </row>
-    <row r="72" spans="1:13">
+      <c r="N71" s="1" t="s">
+        <v>2257</v>
+      </c>
+    </row>
+    <row r="72" spans="1:15" ht="13.5">
       <c r="A72" t="s">
         <v>75</v>
       </c>
@@ -54131,22 +54585,28 @@
         <v>1069</v>
       </c>
       <c r="C72" t="s">
+        <v>2189</v>
+      </c>
+      <c r="D72" t="s">
         <v>2190</v>
       </c>
-      <c r="D72" t="s">
-        <v>2191</v>
-      </c>
       <c r="H72" t="s">
-        <v>2126</v>
-      </c>
-      <c r="L72" t="s">
-        <v>2108</v>
+        <v>2125</v>
+      </c>
+      <c r="L72" s="2" t="s">
+        <v>2258</v>
       </c>
       <c r="M72">
         <v>1</v>
       </c>
-    </row>
-    <row r="73" spans="1:13">
+      <c r="N72" s="1" t="s">
+        <v>2257</v>
+      </c>
+      <c r="O72" s="1" t="s">
+        <v>2260</v>
+      </c>
+    </row>
+    <row r="73" spans="1:15">
       <c r="A73" t="s">
         <v>75</v>
       </c>
@@ -54157,7 +54617,7 @@
         <v>1074</v>
       </c>
       <c r="E73" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="L73" t="s">
         <v>2108</v>
@@ -54165,8 +54625,11 @@
       <c r="M73">
         <v>1</v>
       </c>
-    </row>
-    <row r="74" spans="1:13">
+      <c r="N73" s="1" t="s">
+        <v>2257</v>
+      </c>
+    </row>
+    <row r="74" spans="1:15" ht="13.5">
       <c r="A74" t="s">
         <v>75</v>
       </c>
@@ -54174,25 +54637,31 @@
         <v>1069</v>
       </c>
       <c r="C74" t="s">
+        <v>2191</v>
+      </c>
+      <c r="D74" t="s">
         <v>2192</v>
       </c>
-      <c r="D74" t="s">
-        <v>2193</v>
-      </c>
       <c r="F74" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="H74" t="s">
-        <v>2126</v>
-      </c>
-      <c r="L74" t="s">
-        <v>2108</v>
+        <v>2125</v>
+      </c>
+      <c r="L74" s="2" t="s">
+        <v>2258</v>
       </c>
       <c r="M74">
         <v>1</v>
       </c>
-    </row>
-    <row r="75" spans="1:13">
+      <c r="N74" s="1" t="s">
+        <v>2257</v>
+      </c>
+      <c r="O74" s="1" t="s">
+        <v>2261</v>
+      </c>
+    </row>
+    <row r="75" spans="1:15" ht="13.5">
       <c r="A75" t="s">
         <v>75</v>
       </c>
@@ -54200,25 +54669,31 @@
         <v>1069</v>
       </c>
       <c r="C75" t="s">
+        <v>2193</v>
+      </c>
+      <c r="D75" t="s">
         <v>2194</v>
       </c>
-      <c r="D75" t="s">
-        <v>2195</v>
-      </c>
       <c r="F75" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="H75" t="s">
-        <v>2126</v>
-      </c>
-      <c r="L75" t="s">
-        <v>2108</v>
+        <v>2125</v>
+      </c>
+      <c r="L75" s="2" t="s">
+        <v>2258</v>
       </c>
       <c r="M75">
         <v>1</v>
       </c>
-    </row>
-    <row r="76" spans="1:13">
+      <c r="N75" s="1" t="s">
+        <v>2257</v>
+      </c>
+      <c r="O75" s="1" t="s">
+        <v>2261</v>
+      </c>
+    </row>
+    <row r="76" spans="1:15" ht="13.5">
       <c r="A76" t="s">
         <v>75</v>
       </c>
@@ -54232,19 +54707,25 @@
         <v>1077</v>
       </c>
       <c r="H76" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="J76" t="s">
-        <v>2126</v>
-      </c>
-      <c r="L76" t="s">
-        <v>2108</v>
+        <v>2125</v>
+      </c>
+      <c r="L76" s="2" t="s">
+        <v>2258</v>
       </c>
       <c r="M76">
         <v>1</v>
       </c>
-    </row>
-    <row r="77" spans="1:13">
+      <c r="N76" s="1" t="s">
+        <v>2257</v>
+      </c>
+      <c r="O76" s="1" t="s">
+        <v>2261</v>
+      </c>
+    </row>
+    <row r="77" spans="1:15" ht="13.5">
       <c r="A77" t="s">
         <v>75</v>
       </c>
@@ -54258,19 +54739,25 @@
         <v>1079</v>
       </c>
       <c r="H77" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="J77" t="s">
-        <v>2126</v>
-      </c>
-      <c r="L77" t="s">
-        <v>2108</v>
+        <v>2125</v>
+      </c>
+      <c r="L77" s="2" t="s">
+        <v>2258</v>
       </c>
       <c r="M77">
         <v>1</v>
       </c>
-    </row>
-    <row r="78" spans="1:13">
+      <c r="N77" s="1" t="s">
+        <v>2257</v>
+      </c>
+      <c r="O77" s="1" t="s">
+        <v>2261</v>
+      </c>
+    </row>
+    <row r="78" spans="1:15" ht="13.5">
       <c r="A78" t="s">
         <v>75</v>
       </c>
@@ -54278,28 +54765,34 @@
         <v>1069</v>
       </c>
       <c r="C78" t="s">
+        <v>2195</v>
+      </c>
+      <c r="D78" t="s">
         <v>2196</v>
       </c>
-      <c r="D78" t="s">
-        <v>2197</v>
-      </c>
       <c r="F78" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="H78" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="J78" t="s">
-        <v>2126</v>
-      </c>
-      <c r="L78" t="s">
-        <v>2108</v>
+        <v>2125</v>
+      </c>
+      <c r="L78" s="2" t="s">
+        <v>2258</v>
       </c>
       <c r="M78">
         <v>1</v>
       </c>
-    </row>
-    <row r="79" spans="1:13">
+      <c r="N78" s="1" t="s">
+        <v>2257</v>
+      </c>
+      <c r="O78" s="1" t="s">
+        <v>2261</v>
+      </c>
+    </row>
+    <row r="79" spans="1:15">
       <c r="A79" t="s">
         <v>75</v>
       </c>
@@ -54307,10 +54800,10 @@
         <v>1069</v>
       </c>
       <c r="C79" t="s">
-        <v>2198</v>
+        <v>2197</v>
       </c>
       <c r="E79" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="L79" t="s">
         <v>2108</v>
@@ -54318,8 +54811,11 @@
       <c r="M79">
         <v>1</v>
       </c>
-    </row>
-    <row r="80" spans="1:13">
+      <c r="N79" s="1" t="s">
+        <v>2257</v>
+      </c>
+    </row>
+    <row r="80" spans="1:15" ht="13.5">
       <c r="A80" t="s">
         <v>75</v>
       </c>
@@ -54327,25 +54823,31 @@
         <v>1069</v>
       </c>
       <c r="C80" t="s">
+        <v>2198</v>
+      </c>
+      <c r="D80" t="s">
         <v>2199</v>
       </c>
-      <c r="D80" t="s">
-        <v>2200</v>
-      </c>
       <c r="F80" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="H80" t="s">
-        <v>2126</v>
-      </c>
-      <c r="L80" t="s">
-        <v>2108</v>
+        <v>2125</v>
+      </c>
+      <c r="L80" s="2" t="s">
+        <v>2258</v>
       </c>
       <c r="M80">
         <v>1</v>
       </c>
-    </row>
-    <row r="81" spans="1:13">
+      <c r="N80" s="1" t="s">
+        <v>2257</v>
+      </c>
+      <c r="O80" s="1" t="s">
+        <v>2261</v>
+      </c>
+    </row>
+    <row r="81" spans="1:15" ht="13.5">
       <c r="A81" t="s">
         <v>75</v>
       </c>
@@ -54353,25 +54855,31 @@
         <v>1069</v>
       </c>
       <c r="C81" t="s">
+        <v>2200</v>
+      </c>
+      <c r="D81" t="s">
         <v>2201</v>
       </c>
-      <c r="D81" t="s">
-        <v>2202</v>
-      </c>
       <c r="F81" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="H81" t="s">
-        <v>2126</v>
-      </c>
-      <c r="L81" t="s">
-        <v>2108</v>
+        <v>2125</v>
+      </c>
+      <c r="L81" s="2" t="s">
+        <v>2258</v>
       </c>
       <c r="M81">
         <v>1</v>
       </c>
-    </row>
-    <row r="82" spans="1:13">
+      <c r="N81" s="1" t="s">
+        <v>2257</v>
+      </c>
+      <c r="O81" s="1" t="s">
+        <v>2261</v>
+      </c>
+    </row>
+    <row r="82" spans="1:15" ht="13.5">
       <c r="A82" t="s">
         <v>75</v>
       </c>
@@ -54379,25 +54887,31 @@
         <v>1069</v>
       </c>
       <c r="C82" t="s">
+        <v>2202</v>
+      </c>
+      <c r="D82" t="s">
         <v>2203</v>
       </c>
-      <c r="D82" t="s">
-        <v>2204</v>
-      </c>
       <c r="F82" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="H82" t="s">
-        <v>2126</v>
-      </c>
-      <c r="L82" t="s">
-        <v>2108</v>
+        <v>2125</v>
+      </c>
+      <c r="L82" s="2" t="s">
+        <v>2258</v>
       </c>
       <c r="M82">
         <v>1</v>
       </c>
-    </row>
-    <row r="83" spans="1:13">
+      <c r="N82" s="1" t="s">
+        <v>2257</v>
+      </c>
+      <c r="O82" s="1" t="s">
+        <v>2261</v>
+      </c>
+    </row>
+    <row r="83" spans="1:15">
       <c r="A83" t="s">
         <v>75</v>
       </c>
@@ -54405,10 +54919,10 @@
         <v>1069</v>
       </c>
       <c r="C83" t="s">
-        <v>2205</v>
+        <v>2204</v>
       </c>
       <c r="E83" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="L83" t="s">
         <v>2108</v>
@@ -54416,8 +54930,11 @@
       <c r="M83">
         <v>1</v>
       </c>
-    </row>
-    <row r="84" spans="1:13">
+      <c r="N83" s="1" t="s">
+        <v>2257</v>
+      </c>
+    </row>
+    <row r="84" spans="1:15" ht="13.5">
       <c r="A84" t="s">
         <v>75</v>
       </c>
@@ -54431,22 +54948,28 @@
         <v>1083</v>
       </c>
       <c r="H84" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="I84" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="J84" t="s">
-        <v>2126</v>
-      </c>
-      <c r="L84" t="s">
-        <v>2108</v>
+        <v>2125</v>
+      </c>
+      <c r="L84" s="2" t="s">
+        <v>2258</v>
       </c>
       <c r="M84">
         <v>1</v>
       </c>
-    </row>
-    <row r="85" spans="1:13">
+      <c r="N84" s="1" t="s">
+        <v>2257</v>
+      </c>
+      <c r="O84" s="1" t="s">
+        <v>2262</v>
+      </c>
+    </row>
+    <row r="85" spans="1:15" ht="13.5">
       <c r="A85" t="s">
         <v>75</v>
       </c>
@@ -54454,28 +54977,34 @@
         <v>1069</v>
       </c>
       <c r="C85" t="s">
+        <v>2205</v>
+      </c>
+      <c r="D85" t="s">
         <v>2206</v>
       </c>
-      <c r="D85" t="s">
-        <v>2207</v>
-      </c>
       <c r="F85" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="H85" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="J85" t="s">
-        <v>2126</v>
-      </c>
-      <c r="L85" t="s">
-        <v>2108</v>
+        <v>2125</v>
+      </c>
+      <c r="L85" s="2" t="s">
+        <v>2258</v>
       </c>
       <c r="M85">
         <v>1</v>
       </c>
-    </row>
-    <row r="86" spans="1:13">
+      <c r="N85" s="1" t="s">
+        <v>2257</v>
+      </c>
+      <c r="O85" s="1" t="s">
+        <v>2262</v>
+      </c>
+    </row>
+    <row r="86" spans="1:15" ht="13.5">
       <c r="A86" t="s">
         <v>75</v>
       </c>
@@ -54483,28 +55012,34 @@
         <v>1069</v>
       </c>
       <c r="C86" t="s">
+        <v>2207</v>
+      </c>
+      <c r="D86" t="s">
         <v>2208</v>
       </c>
-      <c r="D86" t="s">
-        <v>2209</v>
-      </c>
       <c r="F86" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="H86" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="I86" t="s">
-        <v>2126</v>
-      </c>
-      <c r="L86" t="s">
-        <v>2108</v>
+        <v>2125</v>
+      </c>
+      <c r="L86" s="2" t="s">
+        <v>2258</v>
       </c>
       <c r="M86">
         <v>1</v>
       </c>
-    </row>
-    <row r="87" spans="1:13">
+      <c r="N86" s="1" t="s">
+        <v>2257</v>
+      </c>
+      <c r="O86" s="1" t="s">
+        <v>2262</v>
+      </c>
+    </row>
+    <row r="87" spans="1:15" ht="13.5">
       <c r="A87" t="s">
         <v>75</v>
       </c>
@@ -54512,31 +55047,37 @@
         <v>1069</v>
       </c>
       <c r="C87" t="s">
+        <v>2209</v>
+      </c>
+      <c r="D87" t="s">
         <v>2210</v>
       </c>
-      <c r="D87" t="s">
-        <v>2211</v>
-      </c>
       <c r="F87" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="H87" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="I87" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="J87" t="s">
-        <v>2126</v>
-      </c>
-      <c r="L87" t="s">
-        <v>2108</v>
+        <v>2125</v>
+      </c>
+      <c r="L87" s="2" t="s">
+        <v>2258</v>
       </c>
       <c r="M87">
         <v>1</v>
       </c>
-    </row>
-    <row r="88" spans="1:13">
+      <c r="N87" s="1" t="s">
+        <v>2257</v>
+      </c>
+      <c r="O87" s="1" t="s">
+        <v>2262</v>
+      </c>
+    </row>
+    <row r="88" spans="1:15" ht="13.5">
       <c r="A88" t="s">
         <v>75</v>
       </c>
@@ -54544,28 +55085,34 @@
         <v>1069</v>
       </c>
       <c r="C88" t="s">
+        <v>2211</v>
+      </c>
+      <c r="D88" t="s">
         <v>2212</v>
       </c>
-      <c r="D88" t="s">
-        <v>2213</v>
-      </c>
       <c r="F88" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="H88" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="I88" t="s">
-        <v>2126</v>
-      </c>
-      <c r="L88" t="s">
-        <v>2108</v>
+        <v>2125</v>
+      </c>
+      <c r="L88" s="2" t="s">
+        <v>2258</v>
       </c>
       <c r="M88">
         <v>1</v>
       </c>
-    </row>
-    <row r="89" spans="1:13">
+      <c r="N88" s="1" t="s">
+        <v>2257</v>
+      </c>
+      <c r="O88" s="1" t="s">
+        <v>2262</v>
+      </c>
+    </row>
+    <row r="89" spans="1:15" ht="13.5">
       <c r="A89" t="s">
         <v>75</v>
       </c>
@@ -54573,28 +55120,34 @@
         <v>1069</v>
       </c>
       <c r="C89" t="s">
+        <v>2213</v>
+      </c>
+      <c r="D89" t="s">
         <v>2214</v>
       </c>
-      <c r="D89" t="s">
-        <v>2215</v>
-      </c>
       <c r="F89" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="H89" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="I89" t="s">
-        <v>2126</v>
-      </c>
-      <c r="L89" t="s">
-        <v>2108</v>
+        <v>2125</v>
+      </c>
+      <c r="L89" s="2" t="s">
+        <v>2258</v>
       </c>
       <c r="M89">
         <v>1</v>
       </c>
-    </row>
-    <row r="90" spans="1:13">
+      <c r="N89" s="1" t="s">
+        <v>2257</v>
+      </c>
+      <c r="O89" s="1" t="s">
+        <v>2262</v>
+      </c>
+    </row>
+    <row r="90" spans="1:15" ht="13.5">
       <c r="A90" t="s">
         <v>75</v>
       </c>
@@ -54602,28 +55155,34 @@
         <v>1069</v>
       </c>
       <c r="C90" t="s">
+        <v>2215</v>
+      </c>
+      <c r="D90" t="s">
         <v>2216</v>
       </c>
-      <c r="D90" t="s">
-        <v>2217</v>
-      </c>
       <c r="F90" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="H90" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="I90" t="s">
-        <v>2126</v>
-      </c>
-      <c r="L90" t="s">
-        <v>2108</v>
+        <v>2125</v>
+      </c>
+      <c r="L90" s="2" t="s">
+        <v>2258</v>
       </c>
       <c r="M90">
         <v>1</v>
       </c>
-    </row>
-    <row r="91" spans="1:13">
+      <c r="N90" s="1" t="s">
+        <v>2257</v>
+      </c>
+      <c r="O90" s="1" t="s">
+        <v>2262</v>
+      </c>
+    </row>
+    <row r="91" spans="1:15">
       <c r="A91" t="s">
         <v>75</v>
       </c>
@@ -54634,7 +55193,7 @@
         <v>1084</v>
       </c>
       <c r="E91" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="L91" t="s">
         <v>2108</v>
@@ -54642,8 +55201,11 @@
       <c r="M91">
         <v>1</v>
       </c>
-    </row>
-    <row r="92" spans="1:13">
+      <c r="N91" s="1" t="s">
+        <v>2257</v>
+      </c>
+    </row>
+    <row r="92" spans="1:15" ht="13.5">
       <c r="A92" t="s">
         <v>75</v>
       </c>
@@ -54651,22 +55213,28 @@
         <v>1069</v>
       </c>
       <c r="C92" t="s">
+        <v>2217</v>
+      </c>
+      <c r="D92" t="s">
         <v>2218</v>
       </c>
-      <c r="D92" t="s">
-        <v>2219</v>
-      </c>
       <c r="H92" t="s">
-        <v>2126</v>
-      </c>
-      <c r="L92" t="s">
-        <v>2108</v>
+        <v>2125</v>
+      </c>
+      <c r="L92" s="2" t="s">
+        <v>2258</v>
       </c>
       <c r="M92">
         <v>1</v>
       </c>
-    </row>
-    <row r="93" spans="1:13">
+      <c r="N92" s="1" t="s">
+        <v>2257</v>
+      </c>
+      <c r="O92" s="1" t="s">
+        <v>2262</v>
+      </c>
+    </row>
+    <row r="93" spans="1:15" ht="13.5">
       <c r="A93" t="s">
         <v>75</v>
       </c>
@@ -54674,22 +55242,28 @@
         <v>1069</v>
       </c>
       <c r="C93" t="s">
+        <v>2219</v>
+      </c>
+      <c r="D93" t="s">
         <v>2220</v>
       </c>
-      <c r="D93" t="s">
-        <v>2221</v>
-      </c>
       <c r="H93" t="s">
-        <v>2126</v>
-      </c>
-      <c r="L93" t="s">
-        <v>2108</v>
+        <v>2125</v>
+      </c>
+      <c r="L93" s="2" t="s">
+        <v>2258</v>
       </c>
       <c r="M93">
         <v>1</v>
       </c>
-    </row>
-    <row r="94" spans="1:13">
+      <c r="N93" s="1" t="s">
+        <v>2257</v>
+      </c>
+      <c r="O93" s="1" t="s">
+        <v>2262</v>
+      </c>
+    </row>
+    <row r="94" spans="1:15" ht="13.5">
       <c r="A94" t="s">
         <v>75</v>
       </c>
@@ -54697,22 +55271,28 @@
         <v>1069</v>
       </c>
       <c r="C94" t="s">
+        <v>2221</v>
+      </c>
+      <c r="D94" t="s">
         <v>2222</v>
       </c>
-      <c r="D94" t="s">
-        <v>2223</v>
-      </c>
       <c r="H94" t="s">
-        <v>2126</v>
-      </c>
-      <c r="L94" t="s">
-        <v>2108</v>
+        <v>2125</v>
+      </c>
+      <c r="L94" s="2" t="s">
+        <v>2258</v>
       </c>
       <c r="M94">
         <v>1</v>
       </c>
-    </row>
-    <row r="95" spans="1:13">
+      <c r="N94" s="1" t="s">
+        <v>2257</v>
+      </c>
+      <c r="O94" s="1" t="s">
+        <v>2262</v>
+      </c>
+    </row>
+    <row r="95" spans="1:15" ht="13.5">
       <c r="A95" t="s">
         <v>75</v>
       </c>
@@ -54720,22 +55300,28 @@
         <v>1171</v>
       </c>
       <c r="C95" t="s">
-        <v>2160</v>
+        <v>2159</v>
       </c>
       <c r="D95" t="s">
-        <v>2224</v>
+        <v>2223</v>
       </c>
       <c r="H95" t="s">
-        <v>2126</v>
-      </c>
-      <c r="L95" t="s">
-        <v>2108</v>
+        <v>2125</v>
+      </c>
+      <c r="L95" s="2" t="s">
+        <v>2258</v>
       </c>
       <c r="M95">
         <v>1</v>
       </c>
-    </row>
-    <row r="96" spans="1:13">
+      <c r="N95" s="1" t="s">
+        <v>2257</v>
+      </c>
+      <c r="O95" s="1" t="s">
+        <v>2262</v>
+      </c>
+    </row>
+    <row r="96" spans="1:15">
       <c r="A96" t="s">
         <v>75</v>
       </c>
@@ -54743,16 +55329,19 @@
         <v>1171</v>
       </c>
       <c r="C96" t="s">
-        <v>2225</v>
+        <v>2224</v>
       </c>
       <c r="E96" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="L96" t="s">
         <v>2108</v>
       </c>
       <c r="M96">
         <v>1</v>
+      </c>
+      <c r="N96" s="1" t="s">
+        <v>2257</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -54763,16 +55352,19 @@
         <v>1171</v>
       </c>
       <c r="C97" t="s">
-        <v>2226</v>
+        <v>2225</v>
       </c>
       <c r="G97" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="L97" t="s">
         <v>2108</v>
       </c>
       <c r="M97">
         <v>1</v>
+      </c>
+      <c r="N97" s="1" t="s">
+        <v>2257</v>
       </c>
     </row>
     <row r="98" spans="1:16" ht="13.5">
@@ -54783,13 +55375,13 @@
         <v>1171</v>
       </c>
       <c r="C98" t="s">
+        <v>2226</v>
+      </c>
+      <c r="D98" t="s">
         <v>2227</v>
       </c>
-      <c r="D98" t="s">
-        <v>2228</v>
-      </c>
       <c r="J98" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="L98" s="2" t="s">
         <v>1590</v>
@@ -54797,8 +55389,11 @@
       <c r="M98">
         <v>1</v>
       </c>
+      <c r="N98" s="1" t="s">
+        <v>2257</v>
+      </c>
       <c r="P98" s="2" t="s">
-        <v>2251</v>
+        <v>2249</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -54809,22 +55404,25 @@
         <v>1171</v>
       </c>
       <c r="C99" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D99" t="s">
         <v>2229</v>
       </c>
-      <c r="D99" t="s">
-        <v>2230</v>
-      </c>
       <c r="J99" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="K99" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="L99" t="s">
         <v>2108</v>
       </c>
       <c r="M99">
         <v>1</v>
+      </c>
+      <c r="N99" s="1" t="s">
+        <v>2257</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -54835,22 +55433,25 @@
         <v>1171</v>
       </c>
       <c r="C100" t="s">
-        <v>2137</v>
+        <v>2136</v>
       </c>
       <c r="D100" t="s">
-        <v>2231</v>
+        <v>2230</v>
       </c>
       <c r="G100" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="J100" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="L100" t="s">
         <v>2108</v>
       </c>
       <c r="M100">
         <v>1</v>
+      </c>
+      <c r="N100" s="1" t="s">
+        <v>2257</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -54861,22 +55462,25 @@
         <v>1171</v>
       </c>
       <c r="C101" t="s">
-        <v>2140</v>
+        <v>2139</v>
       </c>
       <c r="D101" t="s">
-        <v>2232</v>
+        <v>2231</v>
       </c>
       <c r="G101" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="J101" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="L101" t="s">
         <v>2108</v>
       </c>
       <c r="M101">
         <v>1</v>
+      </c>
+      <c r="N101" s="1" t="s">
+        <v>2257</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -54887,16 +55491,19 @@
         <v>1171</v>
       </c>
       <c r="C102" t="s">
-        <v>2233</v>
+        <v>2232</v>
       </c>
       <c r="E102" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="L102" t="s">
         <v>2108</v>
       </c>
       <c r="M102">
         <v>1</v>
+      </c>
+      <c r="N102" s="1" t="s">
+        <v>2257</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -54907,16 +55514,19 @@
         <v>1171</v>
       </c>
       <c r="C103" t="s">
-        <v>2234</v>
+        <v>2233</v>
       </c>
       <c r="E103" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="L103" t="s">
         <v>2108</v>
       </c>
       <c r="M103">
         <v>1</v>
+      </c>
+      <c r="N103" s="1" t="s">
+        <v>2257</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -54927,10 +55537,10 @@
         <v>1171</v>
       </c>
       <c r="C104" t="s">
-        <v>2235</v>
+        <v>2234</v>
       </c>
       <c r="G104" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="L104" t="s">
         <v>2108</v>
@@ -54938,8 +55548,11 @@
       <c r="M104">
         <v>1</v>
       </c>
-    </row>
-    <row r="105" spans="1:16">
+      <c r="N104" s="1" t="s">
+        <v>2257</v>
+      </c>
+    </row>
+    <row r="105" spans="1:16" ht="13.5">
       <c r="A105" t="s">
         <v>75</v>
       </c>
@@ -54953,19 +55566,25 @@
         <v>1173</v>
       </c>
       <c r="H105" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="I105" t="s">
-        <v>2126</v>
-      </c>
-      <c r="L105" t="s">
-        <v>2108</v>
+        <v>2125</v>
+      </c>
+      <c r="L105" s="2" t="s">
+        <v>2258</v>
       </c>
       <c r="M105">
         <v>1</v>
       </c>
-    </row>
-    <row r="106" spans="1:16">
+      <c r="N105" s="1" t="s">
+        <v>2257</v>
+      </c>
+      <c r="O105" s="1" t="s">
+        <v>2262</v>
+      </c>
+    </row>
+    <row r="106" spans="1:16" ht="13.5">
       <c r="A106" t="s">
         <v>75</v>
       </c>
@@ -54973,25 +55592,31 @@
         <v>1171</v>
       </c>
       <c r="C106" t="s">
-        <v>2178</v>
+        <v>2177</v>
       </c>
       <c r="D106" t="s">
-        <v>2236</v>
+        <v>2235</v>
       </c>
       <c r="F106" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="H106" t="s">
-        <v>2126</v>
-      </c>
-      <c r="L106" t="s">
-        <v>2108</v>
+        <v>2125</v>
+      </c>
+      <c r="L106" s="2" t="s">
+        <v>2258</v>
       </c>
       <c r="M106">
         <v>1</v>
       </c>
-    </row>
-    <row r="107" spans="1:16">
+      <c r="N106" s="1" t="s">
+        <v>2257</v>
+      </c>
+      <c r="O106" s="1" t="s">
+        <v>2262</v>
+      </c>
+    </row>
+    <row r="107" spans="1:16" ht="13.5">
       <c r="A107" t="s">
         <v>75</v>
       </c>
@@ -54999,22 +55624,28 @@
         <v>1171</v>
       </c>
       <c r="C107" t="s">
-        <v>2172</v>
+        <v>2171</v>
       </c>
       <c r="D107" t="s">
-        <v>2237</v>
+        <v>2236</v>
       </c>
       <c r="H107" t="s">
-        <v>2126</v>
-      </c>
-      <c r="L107" t="s">
-        <v>2108</v>
+        <v>2125</v>
+      </c>
+      <c r="L107" s="2" t="s">
+        <v>2258</v>
       </c>
       <c r="M107">
         <v>1</v>
       </c>
-    </row>
-    <row r="108" spans="1:16">
+      <c r="N107" s="1" t="s">
+        <v>2257</v>
+      </c>
+      <c r="O107" s="1" t="s">
+        <v>2262</v>
+      </c>
+    </row>
+    <row r="108" spans="1:16" ht="13.5">
       <c r="A108" t="s">
         <v>75</v>
       </c>
@@ -55022,19 +55653,25 @@
         <v>1171</v>
       </c>
       <c r="C108" t="s">
+        <v>2237</v>
+      </c>
+      <c r="D108" t="s">
         <v>2238</v>
       </c>
-      <c r="D108" t="s">
-        <v>2239</v>
-      </c>
       <c r="H108" t="s">
-        <v>2126</v>
-      </c>
-      <c r="L108" t="s">
-        <v>2108</v>
+        <v>2125</v>
+      </c>
+      <c r="L108" s="2" t="s">
+        <v>2258</v>
       </c>
       <c r="M108">
         <v>1</v>
+      </c>
+      <c r="N108" s="1" t="s">
+        <v>2257</v>
+      </c>
+      <c r="O108" s="1" t="s">
+        <v>2262</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -55045,22 +55682,25 @@
         <v>1171</v>
       </c>
       <c r="C109" t="s">
+        <v>2239</v>
+      </c>
+      <c r="D109" t="s">
         <v>2240</v>
       </c>
-      <c r="D109" t="s">
-        <v>2241</v>
-      </c>
       <c r="F109" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="H109" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="L109" t="s">
         <v>2108</v>
       </c>
       <c r="M109">
         <v>1</v>
+      </c>
+      <c r="N109" s="1" t="s">
+        <v>2257</v>
       </c>
     </row>
   </sheetData>
